--- a/AAII_Financials/Quarterly/LGVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGVN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
   <si>
     <t>LGVN</t>
   </si>
@@ -656,88 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43738</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -750,59 +750,62 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E8" s="3">
         <v>200</v>
       </c>
       <c r="F8" s="3">
+        <v>200</v>
+      </c>
+      <c r="G8" s="3">
         <v>300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>400</v>
-      </c>
-      <c r="K8" s="3">
-        <v>200</v>
       </c>
       <c r="L8" s="3">
         <v>200</v>
       </c>
       <c r="M8" s="3">
+        <v>200</v>
+      </c>
+      <c r="N8" s="3">
         <v>500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3800</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -815,8 +818,11 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -827,7 +833,7 @@
         <v>100</v>
       </c>
       <c r="F9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G9" s="3">
         <v>200</v>
@@ -836,38 +842,38 @@
         <v>200</v>
       </c>
       <c r="I9" s="3">
+        <v>200</v>
+      </c>
+      <c r="J9" s="3">
         <v>300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>200</v>
-      </c>
-      <c r="K9" s="3">
-        <v>100</v>
       </c>
       <c r="L9" s="3">
         <v>100</v>
       </c>
       <c r="M9" s="3">
+        <v>100</v>
+      </c>
+      <c r="N9" s="3">
         <v>300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2600</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -880,13 +886,16 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3">
         <v>100</v>
@@ -895,44 +904,44 @@
         <v>100</v>
       </c>
       <c r="G10" s="3">
+        <v>100</v>
+      </c>
+      <c r="H10" s="3">
         <v>-100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>100</v>
-      </c>
-      <c r="I10" s="3">
-        <v>200</v>
       </c>
       <c r="J10" s="3">
         <v>200</v>
       </c>
       <c r="K10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L10" s="3">
         <v>100</v>
       </c>
       <c r="M10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N10" s="3">
         <v>200</v>
       </c>
       <c r="O10" s="3">
+        <v>200</v>
+      </c>
+      <c r="P10" s="3">
         <v>500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1200</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -945,8 +954,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -970,59 +982,60 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E12" s="3">
         <v>1800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1700</v>
-      </c>
-      <c r="L12" s="3">
-        <v>2000</v>
       </c>
       <c r="M12" s="3">
         <v>2000</v>
       </c>
       <c r="N12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O12" s="3">
         <v>1400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1400</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1035,8 +1048,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1100,13 +1116,16 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>300</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1114,8 +1133,8 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -1136,11 +1155,11 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1156,8 +1175,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1165,8 +1184,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1230,8 +1252,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1252,59 +1277,60 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E17" s="3">
         <v>5300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6300</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1317,59 +1343,62 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2500</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1382,8 +1411,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1407,41 +1439,42 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1449,16 +1482,16 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
@@ -1472,59 +1505,62 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-5400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1537,8 +1573,11 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1554,17 +1593,17 @@
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1572,11 +1611,11 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1587,8 +1626,8 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
@@ -1602,59 +1641,62 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2500</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1667,8 +1709,11 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1732,8 +1777,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1797,59 +1845,62 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2500</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1862,59 +1913,62 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2500</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1927,8 +1981,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1992,8 +2049,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2057,8 +2117,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2122,8 +2185,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2187,41 +2253,44 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2229,16 +2298,16 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
@@ -2252,59 +2321,62 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2500</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2317,8 +2389,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2382,59 +2457,62 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2500</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2447,64 +2525,67 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43738</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2517,8 +2598,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2542,8 +2626,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2567,53 +2652,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E41" s="3">
         <v>2000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>22100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>25700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1400</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2632,44 +2718,47 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>400</v>
+      </c>
+      <c r="E42" s="3">
         <v>2000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4600</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2685,8 +2774,8 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2697,8 +2786,11 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2712,13 +2804,13 @@
         <v>100</v>
       </c>
       <c r="G43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H43" s="3">
         <v>200</v>
       </c>
       <c r="I43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J43" s="3">
         <v>100</v>
@@ -2727,23 +2819,23 @@
         <v>100</v>
       </c>
       <c r="L43" s="3">
+        <v>100</v>
+      </c>
+      <c r="M43" s="3">
         <v>200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
       <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
         <v>400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>700</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2762,8 +2854,11 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2827,53 +2922,56 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
         <v>1000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2892,53 +2990,56 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E46" s="3">
         <v>5000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>20300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>23200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>28200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>31900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>35400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>22100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2200</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2957,8 +3058,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3022,8 +3126,11 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3031,44 +3138,44 @@
         <v>3800</v>
       </c>
       <c r="E48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F48" s="3">
         <v>4100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3087,19 +3194,22 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="E49" s="3">
         <v>2500</v>
       </c>
       <c r="F49" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="G49" s="3">
         <v>2400</v>
@@ -3114,16 +3224,16 @@
         <v>2400</v>
       </c>
       <c r="K49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L49" s="3">
         <v>2300</v>
-      </c>
-      <c r="L49" s="3">
-        <v>2400</v>
       </c>
       <c r="M49" s="3">
         <v>2400</v>
       </c>
       <c r="N49" s="3">
-        <v>1500</v>
+        <v>2400</v>
       </c>
       <c r="O49" s="3">
         <v>1500</v>
@@ -3131,8 +3241,8 @@
       <c r="P49" s="3">
         <v>1500</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3">
+        <v>1500</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -3152,8 +3262,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3217,8 +3330,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3282,8 +3398,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3326,8 +3445,8 @@
       <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
+      <c r="Q52" s="3">
+        <v>200</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
@@ -3347,8 +3466,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3412,53 +3534,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E54" s="3">
         <v>11600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>35300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>39200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>42800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9800</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3477,8 +3602,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3502,8 +3630,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3527,53 +3656,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>300</v>
-      </c>
-      <c r="J57" s="3">
-        <v>600</v>
       </c>
       <c r="K57" s="3">
         <v>600</v>
       </c>
       <c r="L57" s="3">
+        <v>600</v>
+      </c>
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1500</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3592,8 +3722,11 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3631,13 +3764,13 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>200</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
+      <c r="Q58" s="3">
+        <v>200</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
@@ -3657,53 +3790,56 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E59" s="3">
         <v>2600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2400</v>
-      </c>
-      <c r="F59" s="3">
-        <v>3100</v>
       </c>
       <c r="G59" s="3">
         <v>3100</v>
       </c>
       <c r="H59" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I59" s="3">
         <v>3200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3722,53 +3858,56 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E60" s="3">
         <v>3400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2900</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3787,8 +3926,11 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3817,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M61" s="3">
         <v>100</v>
@@ -3826,14 +3968,14 @@
         <v>100</v>
       </c>
       <c r="O61" s="3">
+        <v>100</v>
+      </c>
+      <c r="P61" s="3">
         <v>300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>400</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3852,53 +3994,56 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3300</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3917,8 +4062,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3982,8 +4130,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4047,8 +4198,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4112,53 +4266,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E66" s="3">
         <v>5000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6900</v>
-      </c>
-      <c r="H66" s="3">
-        <v>5900</v>
       </c>
       <c r="I66" s="3">
         <v>5900</v>
       </c>
       <c r="J66" s="3">
+        <v>5900</v>
+      </c>
+      <c r="K66" s="3">
         <v>4900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6500</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4177,8 +4334,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4202,8 +4362,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4267,8 +4428,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4332,8 +4496,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4397,8 +4564,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4462,47 +4632,50 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-79000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-73100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-67400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-62800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-58300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-53100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-47400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-43900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-39900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-35000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-30000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4518,8 +4691,8 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V72" s="3">
         <v>0</v>
@@ -4527,8 +4700,11 @@
       <c r="W72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4592,8 +4768,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4657,8 +4836,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4722,53 +4904,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E76" s="3">
         <v>6600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>29400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>34300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>37500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>26500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3300</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4787,8 +4972,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4852,64 +5040,67 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43738</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4922,59 +5113,62 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2500</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4987,8 +5181,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5012,8 +5209,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5045,23 +5243,23 @@
         <v>200</v>
       </c>
       <c r="M83" s="3">
+        <v>200</v>
+      </c>
+      <c r="N83" s="3">
         <v>300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>200</v>
       </c>
       <c r="P83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q83" s="3">
         <v>600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5077,8 +5275,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5142,8 +5343,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5207,8 +5411,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5272,8 +5479,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5337,8 +5547,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5402,56 +5615,59 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-4600</v>
+        <v>-4000</v>
       </c>
       <c r="E89" s="3">
         <v>-4600</v>
       </c>
       <c r="F89" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="G89" s="3">
         <v>-5800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2400</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-3000</v>
       </c>
       <c r="N89" s="3">
         <v>-3000</v>
       </c>
       <c r="O89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>200</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,8 +5683,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5492,55 +5711,56 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1200</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -5557,8 +5777,11 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5622,8 +5845,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5687,55 +5913,58 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E94" s="3">
         <v>3800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1300</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-4700</v>
       </c>
       <c r="M94" s="3">
         <v>-4700</v>
       </c>
       <c r="N94" s="3">
-        <v>0</v>
+        <v>-4700</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5752,8 +5981,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5777,8 +6009,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5842,8 +6075,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5907,8 +6143,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5972,8 +6211,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6037,56 +6279,59 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-100</v>
+        <v>5400</v>
       </c>
       <c r="E100" s="3">
         <v>-100</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3">
         <v>-100</v>
       </c>
       <c r="K100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L100" s="3">
         <v>18500</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>26700</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>1600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6102,8 +6347,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6167,56 +6415,59 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>23600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>300</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6230,6 +6481,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LGVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
   <si>
     <t>LGVN</t>
   </si>
@@ -656,91 +656,92 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -753,62 +754,65 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>500</v>
+      </c>
+      <c r="E8" s="3">
         <v>100</v>
-      </c>
-      <c r="E8" s="3">
-        <v>200</v>
       </c>
       <c r="F8" s="3">
         <v>200</v>
       </c>
       <c r="G8" s="3">
+        <v>200</v>
+      </c>
+      <c r="H8" s="3">
         <v>300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>400</v>
-      </c>
-      <c r="L8" s="3">
-        <v>200</v>
       </c>
       <c r="M8" s="3">
         <v>200</v>
       </c>
       <c r="N8" s="3">
+        <v>200</v>
+      </c>
+      <c r="O8" s="3">
         <v>500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3800</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -821,13 +825,16 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
@@ -836,7 +843,7 @@
         <v>100</v>
       </c>
       <c r="G9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H9" s="3">
         <v>200</v>
@@ -845,38 +852,38 @@
         <v>200</v>
       </c>
       <c r="J9" s="3">
+        <v>200</v>
+      </c>
+      <c r="K9" s="3">
         <v>300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>200</v>
-      </c>
-      <c r="L9" s="3">
-        <v>100</v>
       </c>
       <c r="M9" s="3">
         <v>100</v>
       </c>
       <c r="N9" s="3">
+        <v>100</v>
+      </c>
+      <c r="O9" s="3">
         <v>300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2600</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -889,16 +896,19 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3">
         <v>100</v>
@@ -907,44 +917,44 @@
         <v>100</v>
       </c>
       <c r="H10" s="3">
+        <v>100</v>
+      </c>
+      <c r="I10" s="3">
         <v>-100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>200</v>
       </c>
       <c r="K10" s="3">
         <v>200</v>
       </c>
       <c r="L10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M10" s="3">
         <v>100</v>
       </c>
       <c r="N10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O10" s="3">
         <v>200</v>
       </c>
       <c r="P10" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q10" s="3">
         <v>500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1200</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -957,8 +967,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -983,8 +996,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -992,53 +1006,53 @@
         <v>2200</v>
       </c>
       <c r="E12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F12" s="3">
         <v>1800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1700</v>
-      </c>
-      <c r="M12" s="3">
-        <v>2000</v>
       </c>
       <c r="N12" s="3">
         <v>2000</v>
       </c>
       <c r="O12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P12" s="3">
         <v>1400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1400</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1051,8 +1065,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1119,25 +1136,28 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1158,11 +1178,11 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1178,8 +1198,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1187,8 +1207,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1255,8 +1278,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1278,62 +1304,63 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E17" s="3">
         <v>5800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6300</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1346,62 +1373,65 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2500</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1414,8 +1444,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1440,44 +1473,45 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1485,16 +1519,16 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
@@ -1508,62 +1542,65 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1576,8 +1613,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1596,17 +1636,17 @@
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1614,11 +1654,11 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1629,8 +1669,8 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
@@ -1644,62 +1684,65 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2500</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1712,8 +1755,11 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1780,8 +1826,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1848,62 +1897,65 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2500</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1916,62 +1968,65 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2500</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1984,8 +2039,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2052,8 +2110,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2120,8 +2181,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2188,8 +2252,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2256,44 +2323,47 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2301,16 +2371,16 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
@@ -2324,62 +2394,65 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2500</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2392,8 +2465,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2460,62 +2536,65 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2500</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2528,67 +2607,70 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2601,8 +2683,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2627,8 +2712,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2653,56 +2739,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E41" s="3">
         <v>4900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>22100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>25700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1400</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2721,8 +2808,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2730,38 +2820,38 @@
         <v>400</v>
       </c>
       <c r="E42" s="3">
+        <v>400</v>
+      </c>
+      <c r="F42" s="3">
         <v>2000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4600</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,8 +2867,8 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2789,13 +2879,16 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E43" s="3">
         <v>100</v>
@@ -2807,13 +2900,13 @@
         <v>100</v>
       </c>
       <c r="H43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I43" s="3">
         <v>200</v>
       </c>
       <c r="J43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
@@ -2822,23 +2915,23 @@
         <v>100</v>
       </c>
       <c r="M43" s="3">
+        <v>100</v>
+      </c>
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>700</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2857,8 +2950,11 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2925,56 +3021,59 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2993,56 +3092,59 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E46" s="3">
         <v>5800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>20300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>23200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>28200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>31900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>35400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>19700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>25300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2200</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3061,8 +3163,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3129,56 +3234,59 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3800</v>
+        <v>3500</v>
       </c>
       <c r="E48" s="3">
         <v>3800</v>
       </c>
       <c r="F48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="G48" s="3">
         <v>4100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5900</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3197,8 +3305,11 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3206,13 +3317,13 @@
         <v>2300</v>
       </c>
       <c r="E49" s="3">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="F49" s="3">
         <v>2500</v>
       </c>
       <c r="G49" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="H49" s="3">
         <v>2400</v>
@@ -3227,16 +3338,16 @@
         <v>2400</v>
       </c>
       <c r="L49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="M49" s="3">
         <v>2300</v>
-      </c>
-      <c r="M49" s="3">
-        <v>2400</v>
       </c>
       <c r="N49" s="3">
         <v>2400</v>
       </c>
       <c r="O49" s="3">
-        <v>1500</v>
+        <v>2400</v>
       </c>
       <c r="P49" s="3">
         <v>1500</v>
@@ -3244,8 +3355,8 @@
       <c r="Q49" s="3">
         <v>1500</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
+      <c r="R49" s="3">
+        <v>1500</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
@@ -3265,8 +3376,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3333,8 +3447,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3401,8 +3518,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3448,8 +3568,8 @@
       <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
+      <c r="R52" s="3">
+        <v>200</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
@@ -3469,8 +3589,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3537,56 +3660,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E54" s="3">
         <v>12100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>30500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>35300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>39200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>42800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9800</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3605,8 +3731,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3631,8 +3760,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3657,56 +3787,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>300</v>
-      </c>
-      <c r="K57" s="3">
-        <v>600</v>
       </c>
       <c r="L57" s="3">
         <v>600</v>
       </c>
       <c r="M57" s="3">
+        <v>600</v>
+      </c>
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1500</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,8 +3856,11 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3767,13 +3901,13 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
+      <c r="R58" s="3">
+        <v>200</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
@@ -3793,56 +3927,59 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E59" s="3">
         <v>3300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>3100</v>
       </c>
       <c r="H59" s="3">
         <v>3100</v>
       </c>
       <c r="I59" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J59" s="3">
         <v>3200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1200</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3861,56 +3998,59 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E60" s="3">
         <v>3900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2900</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3929,8 +4069,11 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3962,7 +4105,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>100</v>
@@ -3971,14 +4114,14 @@
         <v>100</v>
       </c>
       <c r="P61" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q61" s="3">
         <v>300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>400</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3997,8 +4140,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4006,47 +4152,47 @@
         <v>1400</v>
       </c>
       <c r="E62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F62" s="3">
         <v>1600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3300</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4065,8 +4211,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4133,8 +4282,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4201,8 +4353,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4269,56 +4424,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E66" s="3">
         <v>5300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6900</v>
-      </c>
-      <c r="I66" s="3">
-        <v>5900</v>
       </c>
       <c r="J66" s="3">
         <v>5900</v>
       </c>
       <c r="K66" s="3">
+        <v>5900</v>
+      </c>
+      <c r="L66" s="3">
         <v>4900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6500</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4337,8 +4495,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4363,8 +4524,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4431,8 +4593,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4499,8 +4664,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4567,8 +4735,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4635,50 +4806,53 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-89000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-85000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-79000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-73100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-67400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-62800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-58300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-53100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-47400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-43900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-39900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-35000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-30000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4694,8 +4868,8 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W72" s="3">
         <v>0</v>
@@ -4703,8 +4877,11 @@
       <c r="X72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4771,8 +4948,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4839,8 +5019,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4907,56 +5090,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>29400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>34300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>37500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>24700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>26500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3300</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4975,8 +5161,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5043,67 +5232,70 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5116,62 +5308,65 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2500</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5184,8 +5379,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5210,13 +5408,14 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3">
         <v>200</v>
@@ -5246,23 +5445,23 @@
         <v>200</v>
       </c>
       <c r="N83" s="3">
+        <v>200</v>
+      </c>
+      <c r="O83" s="3">
         <v>300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>200</v>
       </c>
       <c r="P83" s="3">
         <v>200</v>
       </c>
       <c r="Q83" s="3">
+        <v>200</v>
+      </c>
+      <c r="R83" s="3">
         <v>600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5278,8 +5477,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5346,8 +5548,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5414,8 +5619,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5482,8 +5690,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5550,8 +5761,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5618,59 +5832,62 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4000</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-4600</v>
       </c>
       <c r="F89" s="3">
         <v>-4600</v>
       </c>
       <c r="G89" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="H89" s="3">
         <v>-5800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2400</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-3000</v>
       </c>
       <c r="O89" s="3">
         <v>-3000</v>
       </c>
       <c r="P89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>200</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5686,8 +5903,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5712,58 +5932,59 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1200</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5780,8 +6001,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5848,8 +6072,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5916,58 +6143,61 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>1600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1300</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-4700</v>
       </c>
       <c r="N94" s="3">
         <v>-4700</v>
       </c>
       <c r="O94" s="3">
-        <v>0</v>
+        <v>-4700</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
@@ -5984,8 +6214,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6010,8 +6243,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6078,8 +6312,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6146,8 +6383,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6214,8 +6454,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6282,59 +6525,62 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>5400</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-100</v>
       </c>
       <c r="F100" s="3">
         <v>-100</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K100" s="3">
         <v>-100</v>
       </c>
       <c r="L100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M100" s="3">
         <v>18500</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>26700</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>1600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6350,8 +6596,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6418,59 +6667,62 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E102" s="3">
         <v>3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>23600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>300</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6484,6 +6736,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LGVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
   <si>
     <t>LGVN</t>
   </si>
@@ -656,95 +656,96 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -757,8 +758,11 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -766,56 +770,56 @@
         <v>500</v>
       </c>
       <c r="E8" s="3">
+        <v>500</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
-      </c>
-      <c r="F8" s="3">
-        <v>200</v>
       </c>
       <c r="G8" s="3">
         <v>200</v>
       </c>
       <c r="H8" s="3">
+        <v>200</v>
+      </c>
+      <c r="I8" s="3">
         <v>300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
-      </c>
-      <c r="M8" s="3">
-        <v>200</v>
       </c>
       <c r="N8" s="3">
         <v>200</v>
       </c>
       <c r="O8" s="3">
+        <v>200</v>
+      </c>
+      <c r="P8" s="3">
         <v>500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3800</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -828,16 +832,19 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
         <v>200</v>
-      </c>
-      <c r="E9" s="3">
-        <v>100</v>
       </c>
       <c r="F9" s="3">
         <v>100</v>
@@ -846,7 +853,7 @@
         <v>100</v>
       </c>
       <c r="H9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I9" s="3">
         <v>200</v>
@@ -855,38 +862,38 @@
         <v>200</v>
       </c>
       <c r="K9" s="3">
+        <v>200</v>
+      </c>
+      <c r="L9" s="3">
         <v>300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>200</v>
-      </c>
-      <c r="M9" s="3">
-        <v>100</v>
       </c>
       <c r="N9" s="3">
         <v>100</v>
       </c>
       <c r="O9" s="3">
+        <v>100</v>
+      </c>
+      <c r="P9" s="3">
         <v>300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2600</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -899,19 +906,22 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>400</v>
+      </c>
+      <c r="E10" s="3">
         <v>300</v>
       </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
       <c r="F10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3">
         <v>100</v>
@@ -920,44 +930,44 @@
         <v>100</v>
       </c>
       <c r="I10" s="3">
+        <v>100</v>
+      </c>
+      <c r="J10" s="3">
         <v>-100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>100</v>
-      </c>
-      <c r="K10" s="3">
-        <v>200</v>
       </c>
       <c r="L10" s="3">
         <v>200</v>
       </c>
       <c r="M10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N10" s="3">
         <v>100</v>
       </c>
       <c r="O10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P10" s="3">
         <v>200</v>
       </c>
       <c r="Q10" s="3">
+        <v>200</v>
+      </c>
+      <c r="R10" s="3">
         <v>500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1200</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -970,8 +980,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -997,65 +1010,66 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>2200</v>
+        <v>1700</v>
       </c>
       <c r="E12" s="3">
         <v>2200</v>
       </c>
       <c r="F12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G12" s="3">
         <v>1800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1700</v>
-      </c>
-      <c r="N12" s="3">
-        <v>2000</v>
       </c>
       <c r="O12" s="3">
         <v>2000</v>
       </c>
       <c r="P12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q12" s="3">
         <v>1400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1400</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1068,8 +1082,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1139,28 +1156,31 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1181,11 +1201,11 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1201,8 +1221,8 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1210,8 +1230,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1281,8 +1304,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1305,65 +1331,66 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6300</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1376,65 +1403,68 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2500</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1447,8 +1477,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1474,8 +1507,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1483,38 +1517,38 @@
         <v>100</v>
       </c>
       <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1522,16 +1556,16 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
@@ -1545,65 +1579,68 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-5800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-5400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1616,8 +1653,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1639,17 +1679,17 @@
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1657,11 +1697,11 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1672,8 +1712,8 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -1687,65 +1727,68 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2500</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1758,8 +1801,11 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1829,8 +1875,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1900,65 +1949,68 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2500</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1971,65 +2023,68 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2500</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2042,8 +2097,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2113,8 +2171,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2184,8 +2245,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2255,8 +2319,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2326,8 +2393,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2335,38 +2405,38 @@
         <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2374,16 +2444,16 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
@@ -2397,65 +2467,68 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2500</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2468,8 +2541,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2539,65 +2615,68 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2500</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2610,70 +2689,73 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2686,8 +2768,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2713,8 +2798,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2740,59 +2826,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E41" s="3">
         <v>1900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>20200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>22100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>25700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>24500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1400</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2811,50 +2898,53 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>400</v>
+      <c r="D42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E42" s="3">
         <v>400</v>
       </c>
       <c r="F42" s="3">
+        <v>400</v>
+      </c>
+      <c r="G42" s="3">
         <v>2000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4600</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2870,8 +2960,8 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -2882,8 +2972,11 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2891,7 +2984,7 @@
         <v>200</v>
       </c>
       <c r="E43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F43" s="3">
         <v>100</v>
@@ -2903,13 +2996,13 @@
         <v>100</v>
       </c>
       <c r="I43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J43" s="3">
         <v>200</v>
       </c>
       <c r="K43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L43" s="3">
         <v>100</v>
@@ -2918,23 +3011,23 @@
         <v>100</v>
       </c>
       <c r="N43" s="3">
+        <v>100</v>
+      </c>
+      <c r="O43" s="3">
         <v>200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
         <v>400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>700</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2953,8 +3046,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3024,59 +3120,62 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>800</v>
+      </c>
+      <c r="E45" s="3">
         <v>1300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3095,59 +3194,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E46" s="3">
         <v>3800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>20300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>23200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>28200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>31900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>35400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>19700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>22100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>25300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2200</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3166,8 +3268,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3237,59 +3342,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E48" s="3">
         <v>3500</v>
-      </c>
-      <c r="E48" s="3">
-        <v>3800</v>
       </c>
       <c r="F48" s="3">
         <v>3800</v>
       </c>
       <c r="G48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="H48" s="3">
         <v>4100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5900</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3308,25 +3416,28 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="E49" s="3">
         <v>2300</v>
       </c>
       <c r="F49" s="3">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="G49" s="3">
         <v>2500</v>
       </c>
       <c r="H49" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="I49" s="3">
         <v>2400</v>
@@ -3341,16 +3452,16 @@
         <v>2400</v>
       </c>
       <c r="M49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="N49" s="3">
         <v>2300</v>
-      </c>
-      <c r="N49" s="3">
-        <v>2400</v>
       </c>
       <c r="O49" s="3">
         <v>2400</v>
       </c>
       <c r="P49" s="3">
-        <v>1500</v>
+        <v>2400</v>
       </c>
       <c r="Q49" s="3">
         <v>1500</v>
@@ -3358,8 +3469,8 @@
       <c r="R49" s="3">
         <v>1500</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
+      <c r="S49" s="3">
+        <v>1500</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
@@ -3379,8 +3490,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3450,8 +3564,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3521,8 +3638,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3571,8 +3691,8 @@
       <c r="R52" s="3">
         <v>200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
+      <c r="S52" s="3">
+        <v>200</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
@@ -3592,8 +3712,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3663,59 +3786,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E54" s="3">
         <v>9700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>30500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>35300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>39200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>42800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9800</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3734,8 +3860,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3761,8 +3890,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3788,59 +3918,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>300</v>
-      </c>
-      <c r="L57" s="3">
-        <v>600</v>
       </c>
       <c r="M57" s="3">
         <v>600</v>
       </c>
       <c r="N57" s="3">
+        <v>600</v>
+      </c>
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1500</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3859,8 +3990,11 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3904,13 +4038,13 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
+      <c r="S58" s="3">
+        <v>200</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
@@ -3930,59 +4064,62 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E59" s="3">
         <v>3800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>3100</v>
       </c>
       <c r="I59" s="3">
         <v>3100</v>
       </c>
       <c r="J59" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K59" s="3">
         <v>3200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1200</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4001,59 +4138,62 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E60" s="3">
         <v>5300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2900</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4072,8 +4212,11 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4108,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>100</v>
@@ -4117,14 +4260,14 @@
         <v>100</v>
       </c>
       <c r="Q61" s="3">
+        <v>100</v>
+      </c>
+      <c r="R61" s="3">
         <v>300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>400</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4143,59 +4286,62 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="E62" s="3">
         <v>1400</v>
       </c>
       <c r="F62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G62" s="3">
         <v>1600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3300</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4214,8 +4360,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4285,8 +4434,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4356,8 +4508,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4427,59 +4582,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E66" s="3">
         <v>6700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6900</v>
-      </c>
-      <c r="J66" s="3">
-        <v>5900</v>
       </c>
       <c r="K66" s="3">
         <v>5900</v>
       </c>
       <c r="L66" s="3">
+        <v>5900</v>
+      </c>
+      <c r="M66" s="3">
         <v>4900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6500</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4498,8 +4656,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4525,8 +4686,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4596,8 +4758,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4667,8 +4832,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4738,8 +4906,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4809,53 +4980,56 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-101000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-89000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-85000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-79000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-73100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-67400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-62800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-58300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-53100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-47400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-43900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-39900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-35000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4871,8 +5045,8 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X72" s="3">
         <v>0</v>
@@ -4880,8 +5054,11 @@
       <c r="Y72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4951,8 +5128,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5022,8 +5202,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5093,59 +5276,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E76" s="3">
         <v>3000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>29400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>34300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>37500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>24700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>26500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3300</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5164,8 +5350,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5235,70 +5424,73 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5311,65 +5503,68 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2500</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5382,8 +5577,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5409,16 +5607,17 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
         <v>300</v>
-      </c>
-      <c r="E83" s="3">
-        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
@@ -5448,23 +5647,23 @@
         <v>200</v>
       </c>
       <c r="O83" s="3">
+        <v>200</v>
+      </c>
+      <c r="P83" s="3">
         <v>300</v>
-      </c>
-      <c r="P83" s="3">
-        <v>200</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
       </c>
       <c r="R83" s="3">
+        <v>200</v>
+      </c>
+      <c r="S83" s="3">
         <v>600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>200</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5480,8 +5679,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5551,8 +5753,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5622,8 +5827,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5693,8 +5901,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5764,8 +5975,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5835,62 +6049,65 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4000</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-4600</v>
       </c>
       <c r="G89" s="3">
         <v>-4600</v>
       </c>
       <c r="H89" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-5800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2400</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-3000</v>
       </c>
       <c r="P89" s="3">
         <v>-3000</v>
       </c>
       <c r="Q89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>200</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5906,8 +6123,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5933,61 +6153,62 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
       </c>
       <c r="M91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N91" s="3">
         <v>-1200</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
@@ -6004,8 +6225,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6075,8 +6299,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6146,61 +6373,64 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>1600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>2500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1300</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-4700</v>
       </c>
       <c r="O94" s="3">
         <v>-4700</v>
       </c>
       <c r="P94" s="3">
-        <v>0</v>
+        <v>-4700</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
@@ -6217,8 +6447,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6244,8 +6477,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6315,8 +6549,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6386,8 +6623,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6457,8 +6697,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6528,62 +6771,65 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5400</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-100</v>
       </c>
       <c r="G100" s="3">
         <v>-100</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L100" s="3">
         <v>-100</v>
       </c>
       <c r="M100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N100" s="3">
         <v>18500</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>26700</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>1600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6599,8 +6845,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6670,62 +6919,65 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>23600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>300</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6739,6 +6991,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LGVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="92">
   <si>
     <t>LGVN</t>
   </si>
@@ -656,99 +656,100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -761,68 +762,71 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E8" s="3">
         <v>500</v>
       </c>
       <c r="F8" s="3">
+        <v>500</v>
+      </c>
+      <c r="G8" s="3">
         <v>100</v>
-      </c>
-      <c r="G8" s="3">
-        <v>200</v>
       </c>
       <c r="H8" s="3">
         <v>200</v>
       </c>
       <c r="I8" s="3">
+        <v>200</v>
+      </c>
+      <c r="J8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>400</v>
-      </c>
-      <c r="N8" s="3">
-        <v>200</v>
       </c>
       <c r="O8" s="3">
         <v>200</v>
       </c>
       <c r="P8" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q8" s="3">
         <v>500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3800</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
@@ -835,8 +839,11 @@
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -844,10 +851,10 @@
         <v>100</v>
       </c>
       <c r="E9" s="3">
+        <v>100</v>
+      </c>
+      <c r="F9" s="3">
         <v>200</v>
-      </c>
-      <c r="F9" s="3">
-        <v>100</v>
       </c>
       <c r="G9" s="3">
         <v>100</v>
@@ -856,7 +863,7 @@
         <v>100</v>
       </c>
       <c r="I9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J9" s="3">
         <v>200</v>
@@ -865,38 +872,38 @@
         <v>200</v>
       </c>
       <c r="L9" s="3">
+        <v>200</v>
+      </c>
+      <c r="M9" s="3">
         <v>300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>200</v>
-      </c>
-      <c r="N9" s="3">
-        <v>100</v>
       </c>
       <c r="O9" s="3">
         <v>100</v>
       </c>
       <c r="P9" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="3">
         <v>300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2600</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -909,22 +916,25 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="E10" s="3">
         <v>300</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3">
         <v>100</v>
@@ -933,44 +943,44 @@
         <v>100</v>
       </c>
       <c r="J10" s="3">
+        <v>100</v>
+      </c>
+      <c r="K10" s="3">
         <v>-100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>100</v>
-      </c>
-      <c r="L10" s="3">
-        <v>200</v>
       </c>
       <c r="M10" s="3">
         <v>200</v>
       </c>
       <c r="N10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O10" s="3">
         <v>100</v>
       </c>
       <c r="P10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q10" s="3">
         <v>200</v>
       </c>
       <c r="R10" s="3">
+        <v>200</v>
+      </c>
+      <c r="S10" s="3">
         <v>500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1200</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -983,8 +993,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1011,68 +1024,69 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E12" s="3">
         <v>1700</v>
-      </c>
-      <c r="E12" s="3">
-        <v>2200</v>
       </c>
       <c r="F12" s="3">
         <v>2200</v>
       </c>
       <c r="G12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H12" s="3">
         <v>1800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1700</v>
-      </c>
-      <c r="O12" s="3">
-        <v>2000</v>
       </c>
       <c r="P12" s="3">
         <v>2000</v>
       </c>
       <c r="Q12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="R12" s="3">
         <v>1400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1400</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1085,8 +1099,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1159,8 +1176,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1170,20 +1190,20 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>300</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
+        <v>600</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>-100</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1204,11 +1224,11 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-300</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1224,8 +1244,8 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1233,31 +1253,34 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1307,8 +1330,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1332,68 +1358,69 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E17" s="3">
         <v>4000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4600</v>
       </c>
-      <c r="F17" s="3">
-        <v>5800</v>
-      </c>
       <c r="G17" s="3">
+        <v>5500</v>
+      </c>
+      <c r="H17" s="3">
         <v>5300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6300</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1406,68 +1433,71 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-5700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="J18" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-5100</v>
       </c>
-      <c r="H18" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2500</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1480,8 +1510,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1508,67 +1541,68 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>800</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>800</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3">
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
@@ -1582,68 +1616,71 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3800</v>
       </c>
-      <c r="F21" s="3">
-        <v>-5800</v>
-      </c>
       <c r="G21" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="H21" s="3">
         <v>-4900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="M21" s="3">
         <v>-5400</v>
       </c>
-      <c r="I21" s="3">
-        <v>-4400</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1900</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1656,8 +1693,11 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1682,17 +1722,17 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1700,11 +1740,11 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1715,8 +1755,8 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
@@ -1730,68 +1770,71 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2500</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1804,31 +1847,34 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1878,8 +1924,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1952,68 +2001,71 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2500</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2026,68 +2078,71 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4100</v>
       </c>
-      <c r="F27" s="3">
-        <v>-6800</v>
-      </c>
       <c r="G27" s="3">
-        <v>-5100</v>
+        <v>-6000</v>
       </c>
       <c r="H27" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="I27" s="3">
         <v>-5600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2500</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2100,8 +2155,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2174,8 +2232,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2248,8 +2309,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2322,8 +2386,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2396,67 +2463,70 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>200</v>
+      </c>
+      <c r="H32" s="3">
+        <v>100</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L32" s="3">
+        <v>100</v>
+      </c>
+      <c r="M32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N32" s="3">
+        <v>100</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="K32" s="3">
-        <v>100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>1400</v>
-      </c>
-      <c r="M32" s="3">
-        <v>100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3">
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
@@ -2470,68 +2540,71 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-11900</v>
+        <v>-4400</v>
       </c>
       <c r="E33" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-4100</v>
       </c>
-      <c r="F33" s="3">
-        <v>-6800</v>
-      </c>
       <c r="G33" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="H33" s="3">
         <v>-5100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2500</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2544,8 +2617,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2618,68 +2694,71 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-11900</v>
+        <v>-4400</v>
       </c>
       <c r="E35" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-4100</v>
       </c>
-      <c r="F35" s="3">
-        <v>-6800</v>
-      </c>
       <c r="G35" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="H35" s="3">
         <v>-5100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2500</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2692,73 +2771,76 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2771,8 +2853,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2799,8 +2884,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2827,62 +2913,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E41" s="3">
         <v>12400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>20200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>22100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>25700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>16800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1400</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2901,53 +2988,56 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>400</v>
       </c>
       <c r="G42" s="3">
+        <v>400</v>
+      </c>
+      <c r="H42" s="3">
         <v>2000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4600</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2963,8 +3053,8 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -2975,19 +3065,22 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
       </c>
       <c r="F43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G43" s="3">
         <v>100</v>
@@ -2999,13 +3092,13 @@
         <v>100</v>
       </c>
       <c r="J43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K43" s="3">
         <v>200</v>
       </c>
       <c r="L43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M43" s="3">
         <v>100</v>
@@ -3014,23 +3107,23 @@
         <v>100</v>
       </c>
       <c r="O43" s="3">
+        <v>100</v>
+      </c>
+      <c r="P43" s="3">
         <v>200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>100</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
         <v>400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>700</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3049,31 +3142,34 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3123,62 +3219,65 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
+        <v>400</v>
+      </c>
+      <c r="L45" s="3">
+        <v>700</v>
+      </c>
+      <c r="M45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O45" s="3">
+        <v>300</v>
+      </c>
+      <c r="P45" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>600</v>
+      </c>
+      <c r="R45" s="3">
         <v>800</v>
       </c>
-      <c r="E45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>400</v>
-      </c>
-      <c r="K45" s="3">
-        <v>700</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="M45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="N45" s="3">
-        <v>300</v>
-      </c>
-      <c r="O45" s="3">
-        <v>500</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3">
-        <v>800</v>
-      </c>
-      <c r="R45" s="3">
-        <v>600</v>
-      </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3197,62 +3296,65 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E46" s="3">
         <v>13400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>20300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>28200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>31900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>35400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>19700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>22100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>25300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2200</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3271,31 +3373,34 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3345,62 +3450,65 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3500</v>
-      </c>
-      <c r="F48" s="3">
-        <v>3800</v>
       </c>
       <c r="G48" s="3">
         <v>3800</v>
       </c>
       <c r="H48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I48" s="3">
         <v>4100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5900</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3419,28 +3527,31 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E49" s="3">
         <v>2400</v>
-      </c>
-      <c r="E49" s="3">
-        <v>2300</v>
       </c>
       <c r="F49" s="3">
         <v>2300</v>
       </c>
       <c r="G49" s="3">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="H49" s="3">
         <v>2500</v>
       </c>
       <c r="I49" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="J49" s="3">
         <v>2400</v>
@@ -3455,16 +3566,16 @@
         <v>2400</v>
       </c>
       <c r="N49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="O49" s="3">
         <v>2300</v>
-      </c>
-      <c r="O49" s="3">
-        <v>2400</v>
       </c>
       <c r="P49" s="3">
         <v>2400</v>
       </c>
       <c r="Q49" s="3">
-        <v>1500</v>
+        <v>2400</v>
       </c>
       <c r="R49" s="3">
         <v>1500</v>
@@ -3472,8 +3583,8 @@
       <c r="S49" s="3">
         <v>1500</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
+      <c r="T49" s="3">
+        <v>1500</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
@@ -3493,8 +3604,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3567,8 +3681,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3641,8 +3758,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3694,8 +3814,8 @@
       <c r="S52" s="3">
         <v>200</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
+      <c r="T52" s="3">
+        <v>200</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
@@ -3715,8 +3835,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3789,62 +3912,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E54" s="3">
         <v>19400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>30500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>39200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>42800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>27200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9800</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,8 +3989,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3891,8 +4020,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3919,62 +4049,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>300</v>
-      </c>
-      <c r="M57" s="3">
-        <v>600</v>
       </c>
       <c r="N57" s="3">
         <v>600</v>
       </c>
       <c r="O57" s="3">
+        <v>600</v>
+      </c>
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1500</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3993,31 +4124,34 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4041,13 +4175,13 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S58" s="3">
         <v>200</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3">
+        <v>200</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
@@ -4067,62 +4201,65 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2600</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
-        <v>3800</v>
+        <v>400</v>
       </c>
       <c r="F59" s="3">
+        <v>800</v>
+      </c>
+      <c r="G59" s="3">
+        <v>500</v>
+      </c>
+      <c r="H59" s="3">
+        <v>500</v>
+      </c>
+      <c r="I59" s="3">
+        <v>500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K59" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M59" s="3">
         <v>3300</v>
       </c>
-      <c r="G59" s="3">
-        <v>2600</v>
-      </c>
-      <c r="H59" s="3">
-        <v>2400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>3100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>3100</v>
-      </c>
-      <c r="K59" s="3">
-        <v>3200</v>
-      </c>
-      <c r="L59" s="3">
-        <v>3300</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1200</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4141,62 +4278,65 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E60" s="3">
         <v>3200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2900</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4215,31 +4355,34 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4254,7 +4397,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>100</v>
@@ -4263,14 +4406,14 @@
         <v>100</v>
       </c>
       <c r="R61" s="3">
+        <v>100</v>
+      </c>
+      <c r="S61" s="3">
         <v>300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>400</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4289,62 +4432,65 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1300</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
-        <v>1400</v>
+        <v>100</v>
       </c>
       <c r="F62" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1900</v>
-      </c>
-      <c r="J62" s="3">
+        <v>100</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>2000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3300</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4363,8 +4509,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4437,8 +4586,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4511,8 +4663,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4585,62 +4740,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E66" s="3">
         <v>4500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6900</v>
-      </c>
-      <c r="K66" s="3">
-        <v>5900</v>
       </c>
       <c r="L66" s="3">
         <v>5900</v>
       </c>
       <c r="M66" s="3">
+        <v>5900</v>
+      </c>
+      <c r="N66" s="3">
         <v>4900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6500</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4659,8 +4817,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4687,8 +4848,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4761,8 +4923,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4835,8 +5000,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4909,8 +5077,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4983,56 +5154,59 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-105500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-101000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-89000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-85000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-79000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-73100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-67400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-62800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-58300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-53100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-47400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-43900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-39900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-35000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-30000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5048,8 +5222,8 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X72" s="3">
-        <v>0</v>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y72" s="3">
         <v>0</v>
@@ -5057,8 +5231,11 @@
       <c r="Z72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5131,8 +5308,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5205,8 +5385,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5279,62 +5462,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E76" s="3">
         <v>14900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>29400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>34300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>37500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>24700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>26500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3300</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5353,8 +5539,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5427,73 +5616,76 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5506,68 +5698,71 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-11900</v>
+        <v>-4400</v>
       </c>
       <c r="E81" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-4100</v>
       </c>
-      <c r="F81" s="3">
-        <v>-6800</v>
-      </c>
       <c r="G81" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="H81" s="3">
         <v>-5100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2500</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5580,8 +5775,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5608,8 +5806,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5617,7 +5816,7 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
@@ -5632,7 +5831,7 @@
         <v>200</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
@@ -5650,23 +5849,23 @@
         <v>200</v>
       </c>
       <c r="P83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q83" s="3">
         <v>300</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>200</v>
       </c>
       <c r="R83" s="3">
         <v>200</v>
       </c>
       <c r="S83" s="3">
+        <v>200</v>
+      </c>
+      <c r="T83" s="3">
         <v>600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>200</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5682,8 +5881,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5756,8 +5958,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5830,8 +6035,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5904,8 +6112,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5978,8 +6189,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6052,65 +6266,68 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4000</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-4600</v>
       </c>
       <c r="H89" s="3">
         <v>-4600</v>
       </c>
       <c r="I89" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-5800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2400</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-3000</v>
       </c>
       <c r="Q89" s="3">
         <v>-3000</v>
       </c>
       <c r="R89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>200</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6126,8 +6343,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6154,64 +6374,65 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="H91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-100</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
       </c>
       <c r="N91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O91" s="3">
         <v>-1200</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
@@ -6228,8 +6449,11 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6302,8 +6526,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6376,64 +6603,67 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>1600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>2500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-4700</v>
       </c>
       <c r="P94" s="3">
         <v>-4700</v>
       </c>
       <c r="Q94" s="3">
-        <v>0</v>
+        <v>-4700</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
@@ -6450,8 +6680,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6478,31 +6711,32 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6552,8 +6786,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6626,8 +6863,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6700,8 +6940,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6774,65 +7017,68 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E100" s="3">
         <v>15100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5400</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-100</v>
       </c>
       <c r="H100" s="3">
         <v>-100</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M100" s="3">
         <v>-100</v>
       </c>
       <c r="N100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O100" s="3">
         <v>18500</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>26700</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>1600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6848,31 +7094,34 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6922,8 +7171,11 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6931,56 +7183,56 @@
         <v>10400</v>
       </c>
       <c r="E102" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>23600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>300</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6994,6 +7246,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LGVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="92">
   <si>
     <t>LGVN</t>
   </si>
@@ -656,103 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -765,71 +765,74 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>600</v>
+      </c>
+      <c r="E8" s="3">
         <v>800</v>
-      </c>
-      <c r="E8" s="3">
-        <v>500</v>
       </c>
       <c r="F8" s="3">
         <v>500</v>
       </c>
       <c r="G8" s="3">
+        <v>500</v>
+      </c>
+      <c r="H8" s="3">
         <v>100</v>
-      </c>
-      <c r="H8" s="3">
-        <v>200</v>
       </c>
       <c r="I8" s="3">
         <v>200</v>
       </c>
       <c r="J8" s="3">
+        <v>200</v>
+      </c>
+      <c r="K8" s="3">
         <v>300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>400</v>
-      </c>
-      <c r="O8" s="3">
-        <v>200</v>
       </c>
       <c r="P8" s="3">
         <v>200</v>
       </c>
       <c r="Q8" s="3">
+        <v>200</v>
+      </c>
+      <c r="R8" s="3">
         <v>500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3800</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
@@ -842,8 +845,11 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -854,10 +860,10 @@
         <v>100</v>
       </c>
       <c r="F9" s="3">
+        <v>100</v>
+      </c>
+      <c r="G9" s="3">
         <v>200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>100</v>
       </c>
       <c r="H9" s="3">
         <v>100</v>
@@ -866,7 +872,7 @@
         <v>100</v>
       </c>
       <c r="J9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K9" s="3">
         <v>200</v>
@@ -875,38 +881,38 @@
         <v>200</v>
       </c>
       <c r="M9" s="3">
+        <v>200</v>
+      </c>
+      <c r="N9" s="3">
         <v>300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>200</v>
-      </c>
-      <c r="O9" s="3">
-        <v>100</v>
       </c>
       <c r="P9" s="3">
         <v>100</v>
       </c>
       <c r="Q9" s="3">
+        <v>100</v>
+      </c>
+      <c r="R9" s="3">
         <v>300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2600</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
@@ -919,25 +925,28 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>500</v>
+      </c>
+      <c r="E10" s="3">
         <v>700</v>
-      </c>
-      <c r="E10" s="3">
-        <v>300</v>
       </c>
       <c r="F10" s="3">
         <v>300</v>
       </c>
       <c r="G10" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3">
         <v>100</v>
@@ -946,44 +955,44 @@
         <v>100</v>
       </c>
       <c r="K10" s="3">
+        <v>100</v>
+      </c>
+      <c r="L10" s="3">
         <v>-100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>100</v>
-      </c>
-      <c r="M10" s="3">
-        <v>200</v>
       </c>
       <c r="N10" s="3">
         <v>200</v>
       </c>
       <c r="O10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P10" s="3">
         <v>100</v>
       </c>
       <c r="Q10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R10" s="3">
         <v>200</v>
       </c>
       <c r="S10" s="3">
+        <v>200</v>
+      </c>
+      <c r="T10" s="3">
         <v>500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1200</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
@@ -996,8 +1005,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1025,71 +1037,72 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E12" s="3">
         <v>2200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1700</v>
-      </c>
-      <c r="F12" s="3">
-        <v>2200</v>
       </c>
       <c r="G12" s="3">
         <v>2200</v>
       </c>
       <c r="H12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I12" s="3">
         <v>1800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1700</v>
-      </c>
-      <c r="P12" s="3">
-        <v>2000</v>
       </c>
       <c r="Q12" s="3">
         <v>2000</v>
       </c>
       <c r="R12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="S12" s="3">
         <v>1400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1400</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1102,8 +1115,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1179,8 +1195,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1193,20 +1212,20 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>600</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-100</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
         <v>-100</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1227,11 +1246,11 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-300</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1247,8 +1266,8 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1256,8 +1275,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1268,10 +1290,10 @@
         <v>200</v>
       </c>
       <c r="F15" s="3">
+        <v>200</v>
+      </c>
+      <c r="G15" s="3">
         <v>300</v>
-      </c>
-      <c r="G15" s="3">
-        <v>200</v>
       </c>
       <c r="H15" s="3">
         <v>200</v>
@@ -1283,7 +1305,7 @@
         <v>200</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1333,8 +1355,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1359,71 +1384,72 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E17" s="3">
         <v>5400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6300</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1436,71 +1462,74 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2500</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1513,8 +1542,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1542,53 +1574,54 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1596,16 +1629,16 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
@@ -1619,71 +1652,74 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="M21" s="3">
         <v>-5000</v>
       </c>
-      <c r="H21" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1900</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1696,8 +1732,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1725,17 +1764,17 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1743,11 +1782,11 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1758,8 +1797,8 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
@@ -1773,71 +1812,74 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2500</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1850,8 +1892,11 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1876,8 +1921,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1927,8 +1972,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2004,71 +2052,74 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2500</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2081,71 +2132,74 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2500</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2158,8 +2212,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2235,8 +2292,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2312,8 +2372,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2389,8 +2452,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2466,53 +2532,56 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2520,16 +2589,16 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
@@ -2543,71 +2612,74 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2500</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2620,8 +2692,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2697,71 +2772,74 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2500</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2774,76 +2852,79 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2856,8 +2937,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2885,8 +2969,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2914,65 +2999,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E41" s="3">
         <v>22800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>22100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>25700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>16800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1400</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2991,8 +3077,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3003,44 +3092,44 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>400</v>
       </c>
       <c r="H42" s="3">
+        <v>400</v>
+      </c>
+      <c r="I42" s="3">
         <v>2000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>8400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>9200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>4600</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3056,8 +3145,8 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3068,22 +3157,25 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>100</v>
+      </c>
+      <c r="E43" s="3">
         <v>400</v>
-      </c>
-      <c r="E43" s="3">
-        <v>200</v>
       </c>
       <c r="F43" s="3">
         <v>200</v>
       </c>
       <c r="G43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H43" s="3">
         <v>100</v>
@@ -3095,13 +3187,13 @@
         <v>100</v>
       </c>
       <c r="K43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L43" s="3">
         <v>200</v>
       </c>
       <c r="M43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N43" s="3">
         <v>100</v>
@@ -3110,23 +3202,23 @@
         <v>100</v>
       </c>
       <c r="P43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
       <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
         <v>400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>700</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3145,8 +3237,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3171,8 +3266,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3222,8 +3317,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3248,39 +3346,39 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3299,65 +3397,68 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E46" s="3">
         <v>23800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>20300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>28200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>31900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>35400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>19700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>22100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>25300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2200</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3376,8 +3477,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3402,8 +3506,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3453,65 +3557,68 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E48" s="3">
         <v>3600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3500</v>
-      </c>
-      <c r="G48" s="3">
-        <v>3800</v>
       </c>
       <c r="H48" s="3">
         <v>3800</v>
       </c>
       <c r="I48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J48" s="3">
         <v>4100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5900</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3530,31 +3637,34 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E49" s="3">
         <v>2300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2400</v>
-      </c>
-      <c r="F49" s="3">
-        <v>2300</v>
       </c>
       <c r="G49" s="3">
         <v>2300</v>
       </c>
       <c r="H49" s="3">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="I49" s="3">
         <v>2500</v>
       </c>
       <c r="J49" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="K49" s="3">
         <v>2400</v>
@@ -3569,16 +3679,16 @@
         <v>2400</v>
       </c>
       <c r="O49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="P49" s="3">
         <v>2300</v>
-      </c>
-      <c r="P49" s="3">
-        <v>2400</v>
       </c>
       <c r="Q49" s="3">
         <v>2400</v>
       </c>
       <c r="R49" s="3">
-        <v>1500</v>
+        <v>2400</v>
       </c>
       <c r="S49" s="3">
         <v>1500</v>
@@ -3586,8 +3696,8 @@
       <c r="T49" s="3">
         <v>1500</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
+      <c r="U49" s="3">
+        <v>1500</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
@@ -3607,8 +3717,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3684,8 +3797,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3761,8 +3877,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3817,8 +3936,8 @@
       <c r="T52" s="3">
         <v>200</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
+      <c r="U52" s="3">
+        <v>200</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
@@ -3838,8 +3957,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3915,65 +4037,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E54" s="3">
         <v>29900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>30500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>35300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>39200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>42800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>27200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>29900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>32400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9800</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3992,8 +4117,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4021,8 +4149,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4050,65 +4179,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
-      </c>
-      <c r="N57" s="3">
-        <v>600</v>
       </c>
       <c r="O57" s="3">
         <v>600</v>
       </c>
       <c r="P57" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q57" s="3">
         <v>400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1500</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4127,8 +4257,11 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4154,7 +4287,7 @@
         <v>600</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -4178,13 +4311,13 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
         <v>200</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
+      <c r="U58" s="3">
+        <v>200</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
@@ -4204,22 +4337,25 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
         <v>100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>800</v>
-      </c>
-      <c r="G59" s="3">
-        <v>500</v>
       </c>
       <c r="H59" s="3">
         <v>500</v>
@@ -4228,41 +4364,41 @@
         <v>500</v>
       </c>
       <c r="J59" s="3">
+        <v>500</v>
+      </c>
+      <c r="K59" s="3">
         <v>2000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1200</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4281,65 +4417,68 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E60" s="3">
         <v>3100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2900</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4358,35 +4497,38 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>800</v>
+      </c>
+      <c r="E61" s="3">
         <v>1000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4400,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>100</v>
@@ -4409,14 +4551,14 @@
         <v>100</v>
       </c>
       <c r="S61" s="3">
+        <v>100</v>
+      </c>
+      <c r="T61" s="3">
         <v>300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>400</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4435,22 +4577,25 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>300</v>
+      </c>
+      <c r="E62" s="3">
         <v>200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>100</v>
       </c>
       <c r="F62" s="3">
         <v>100</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
+      <c r="G62" s="3">
+        <v>100</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -4461,39 +4606,39 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>2000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3300</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4512,8 +4657,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4589,8 +4737,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4666,8 +4817,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4743,65 +4897,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E66" s="3">
         <v>4300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6900</v>
-      </c>
-      <c r="L66" s="3">
-        <v>5900</v>
       </c>
       <c r="M66" s="3">
         <v>5900</v>
       </c>
       <c r="N66" s="3">
+        <v>5900</v>
+      </c>
+      <c r="O66" s="3">
         <v>4900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6500</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4820,8 +4977,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4849,8 +5009,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4926,8 +5087,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5003,8 +5167,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5080,8 +5247,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5157,59 +5327,62 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-109600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-105500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-101000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-89000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-85000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-79000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-73100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-67400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-62800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-58300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-53100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-47400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-43900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-39900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-35000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-30000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5225,8 +5398,8 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y72" s="3">
-        <v>0</v>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z72" s="3">
         <v>0</v>
@@ -5234,8 +5407,11 @@
       <c r="AA72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5311,8 +5487,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5388,8 +5567,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5465,65 +5647,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E76" s="3">
         <v>25600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>24600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>29400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>34300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>37500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>24700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>26500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3300</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5542,8 +5727,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5619,76 +5807,79 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5701,71 +5892,74 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2500</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5778,8 +5972,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5807,8 +6004,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5831,10 +6029,10 @@
         <v>200</v>
       </c>
       <c r="J83" s="3">
+        <v>200</v>
+      </c>
+      <c r="K83" s="3">
         <v>100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>200</v>
       </c>
       <c r="L83" s="3">
         <v>200</v>
@@ -5852,23 +6050,23 @@
         <v>200</v>
       </c>
       <c r="Q83" s="3">
+        <v>200</v>
+      </c>
+      <c r="R83" s="3">
         <v>300</v>
-      </c>
-      <c r="R83" s="3">
-        <v>200</v>
       </c>
       <c r="S83" s="3">
         <v>200</v>
       </c>
       <c r="T83" s="3">
+        <v>200</v>
+      </c>
+      <c r="U83" s="3">
         <v>600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>200</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5884,8 +6082,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5961,8 +6162,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6038,8 +6242,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6115,8 +6322,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6192,8 +6402,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6269,68 +6482,71 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4000</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-4600</v>
       </c>
       <c r="I89" s="3">
         <v>-4600</v>
       </c>
       <c r="J89" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="K89" s="3">
         <v>-5800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2400</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-3000</v>
       </c>
       <c r="R89" s="3">
         <v>-3000</v>
       </c>
       <c r="S89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>200</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6346,8 +6562,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6375,67 +6594,68 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1200</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -6452,8 +6672,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6529,8 +6752,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6606,67 +6832,70 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>1600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1300</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-4700</v>
       </c>
       <c r="Q94" s="3">
         <v>-4700</v>
       </c>
       <c r="R94" s="3">
-        <v>0</v>
+        <v>-4700</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
@@ -6683,8 +6912,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6712,8 +6944,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6738,8 +6971,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6789,8 +7022,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6866,8 +7102,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6943,8 +7182,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7020,68 +7262,71 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>13700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>15100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5400</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-100</v>
       </c>
       <c r="I100" s="3">
         <v>-100</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N100" s="3">
         <v>-100</v>
       </c>
       <c r="O100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P100" s="3">
         <v>18500</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>26700</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>1600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7097,8 +7342,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7123,8 +7371,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7174,68 +7422,71 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>10400</v>
+        <v>-3500</v>
       </c>
       <c r="E102" s="3">
         <v>10400</v>
       </c>
       <c r="F102" s="3">
+        <v>10400</v>
+      </c>
+      <c r="G102" s="3">
         <v>-3000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-7600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>23600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>300</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7249,6 +7500,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LGVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="92">
   <si>
     <t>LGVN</t>
   </si>
@@ -656,106 +656,107 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -768,74 +769,77 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>400</v>
+      </c>
+      <c r="E8" s="3">
         <v>600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>800</v>
-      </c>
-      <c r="F8" s="3">
-        <v>500</v>
       </c>
       <c r="G8" s="3">
         <v>500</v>
       </c>
       <c r="H8" s="3">
+        <v>500</v>
+      </c>
+      <c r="I8" s="3">
         <v>100</v>
-      </c>
-      <c r="I8" s="3">
-        <v>200</v>
       </c>
       <c r="J8" s="3">
         <v>200</v>
       </c>
       <c r="K8" s="3">
+        <v>200</v>
+      </c>
+      <c r="L8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>400</v>
-      </c>
-      <c r="P8" s="3">
-        <v>200</v>
       </c>
       <c r="Q8" s="3">
         <v>200</v>
       </c>
       <c r="R8" s="3">
+        <v>200</v>
+      </c>
+      <c r="S8" s="3">
         <v>500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3800</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
@@ -848,8 +852,11 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -863,10 +870,10 @@
         <v>100</v>
       </c>
       <c r="G9" s="3">
+        <v>100</v>
+      </c>
+      <c r="H9" s="3">
         <v>200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>100</v>
       </c>
       <c r="I9" s="3">
         <v>100</v>
@@ -875,7 +882,7 @@
         <v>100</v>
       </c>
       <c r="K9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L9" s="3">
         <v>200</v>
@@ -884,38 +891,38 @@
         <v>200</v>
       </c>
       <c r="N9" s="3">
+        <v>200</v>
+      </c>
+      <c r="O9" s="3">
         <v>300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>200</v>
-      </c>
-      <c r="P9" s="3">
-        <v>100</v>
       </c>
       <c r="Q9" s="3">
         <v>100</v>
       </c>
       <c r="R9" s="3">
+        <v>100</v>
+      </c>
+      <c r="S9" s="3">
         <v>300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2600</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -928,28 +935,31 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>300</v>
+      </c>
+      <c r="E10" s="3">
         <v>500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>700</v>
-      </c>
-      <c r="F10" s="3">
-        <v>300</v>
       </c>
       <c r="G10" s="3">
         <v>300</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3">
         <v>100</v>
@@ -958,44 +968,44 @@
         <v>100</v>
       </c>
       <c r="L10" s="3">
+        <v>100</v>
+      </c>
+      <c r="M10" s="3">
         <v>-100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>100</v>
-      </c>
-      <c r="N10" s="3">
-        <v>200</v>
       </c>
       <c r="O10" s="3">
         <v>200</v>
       </c>
       <c r="P10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q10" s="3">
         <v>100</v>
       </c>
       <c r="R10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S10" s="3">
         <v>200</v>
       </c>
       <c r="T10" s="3">
+        <v>200</v>
+      </c>
+      <c r="U10" s="3">
         <v>500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1200</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1008,8 +1018,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1038,74 +1051,75 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E12" s="3">
         <v>2000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1700</v>
-      </c>
-      <c r="G12" s="3">
-        <v>2200</v>
       </c>
       <c r="H12" s="3">
         <v>2200</v>
       </c>
       <c r="I12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J12" s="3">
         <v>1800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1700</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>2000</v>
       </c>
       <c r="R12" s="3">
         <v>2000</v>
       </c>
       <c r="S12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T12" s="3">
         <v>1400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1400</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1118,8 +1132,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1198,8 +1215,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1215,20 +1235,20 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>600</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
-        <v>-100</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>-100</v>
       </c>
       <c r="L14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1249,11 +1269,11 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-300</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,8 +1289,8 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1278,13 +1298,16 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
@@ -1293,10 +1316,10 @@
         <v>200</v>
       </c>
       <c r="G15" s="3">
+        <v>200</v>
+      </c>
+      <c r="H15" s="3">
         <v>300</v>
-      </c>
-      <c r="H15" s="3">
-        <v>200</v>
       </c>
       <c r="I15" s="3">
         <v>200</v>
@@ -1308,7 +1331,7 @@
         <v>200</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1358,8 +1381,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1385,74 +1411,75 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E17" s="3">
         <v>4900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6300</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1465,74 +1492,77 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2500</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1545,8 +1575,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1575,56 +1608,57 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="E20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1632,16 +1666,16 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
+      <c r="X20" s="3">
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
@@ -1655,74 +1689,77 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1900</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1735,8 +1772,11 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1767,17 +1807,17 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1785,11 +1825,11 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1800,8 +1840,8 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
@@ -1815,74 +1855,77 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2500</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1895,8 +1938,11 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1924,8 +1970,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1975,8 +2021,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2055,74 +2104,77 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2500</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2135,74 +2187,77 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2500</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2215,8 +2270,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2295,8 +2353,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2375,8 +2436,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2455,8 +2519,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2535,56 +2602,59 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="E32" s="3">
+        <v>200</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2592,16 +2662,16 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
+      <c r="X32" s="3">
+        <v>0</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
@@ -2615,74 +2685,77 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2500</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2695,8 +2768,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2775,74 +2851,77 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2500</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,79 +2934,82 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2940,8 +3022,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2970,8 +3055,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3000,68 +3086,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E41" s="3">
         <v>19200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>20200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>22100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>25700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>16800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>24500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1400</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3080,8 +3167,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3095,44 +3185,44 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>400</v>
       </c>
       <c r="I42" s="3">
+        <v>400</v>
+      </c>
+      <c r="J42" s="3">
         <v>2000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>6800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>8400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>9400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>9200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4600</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3148,8 +3238,8 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3160,25 +3250,28 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>400</v>
-      </c>
-      <c r="F43" s="3">
-        <v>200</v>
       </c>
       <c r="G43" s="3">
         <v>200</v>
       </c>
       <c r="H43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3">
         <v>100</v>
@@ -3190,13 +3283,13 @@
         <v>100</v>
       </c>
       <c r="L43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M43" s="3">
         <v>200</v>
       </c>
       <c r="N43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O43" s="3">
         <v>100</v>
@@ -3205,23 +3298,23 @@
         <v>100</v>
       </c>
       <c r="Q43" s="3">
+        <v>100</v>
+      </c>
+      <c r="R43" s="3">
         <v>200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>100</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
         <v>400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>700</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3240,8 +3333,11 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3269,8 +3365,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3320,8 +3416,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3349,39 +3448,39 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3400,68 +3499,71 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E46" s="3">
         <v>19600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>20300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>28200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>31900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>35400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>19700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>22100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>25300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2200</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,8 +3582,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3509,8 +3614,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3560,68 +3665,71 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3500</v>
-      </c>
-      <c r="H48" s="3">
-        <v>3800</v>
       </c>
       <c r="I48" s="3">
         <v>3800</v>
       </c>
       <c r="J48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K48" s="3">
         <v>4100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5900</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3640,34 +3748,37 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E49" s="3">
         <v>2400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2400</v>
-      </c>
-      <c r="G49" s="3">
-        <v>2300</v>
       </c>
       <c r="H49" s="3">
         <v>2300</v>
       </c>
       <c r="I49" s="3">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="J49" s="3">
         <v>2500</v>
       </c>
       <c r="K49" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="L49" s="3">
         <v>2400</v>
@@ -3682,16 +3793,16 @@
         <v>2400</v>
       </c>
       <c r="P49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Q49" s="3">
         <v>2300</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>2400</v>
       </c>
       <c r="R49" s="3">
         <v>2400</v>
       </c>
       <c r="S49" s="3">
-        <v>1500</v>
+        <v>2400</v>
       </c>
       <c r="T49" s="3">
         <v>1500</v>
@@ -3699,8 +3810,8 @@
       <c r="U49" s="3">
         <v>1500</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
+      <c r="V49" s="3">
+        <v>1500</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
@@ -3720,8 +3831,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3800,8 +3914,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3880,8 +3997,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3939,8 +4059,8 @@
       <c r="U52" s="3">
         <v>200</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
+      <c r="V52" s="3">
+        <v>200</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
@@ -3960,8 +4080,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4040,68 +4163,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E54" s="3">
         <v>25600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>29900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>30500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>39200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>42800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>27200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>29900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>32400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9800</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4120,8 +4246,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4150,8 +4279,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4180,68 +4310,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
         <v>100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
-      </c>
-      <c r="O57" s="3">
-        <v>600</v>
       </c>
       <c r="P57" s="3">
         <v>600</v>
       </c>
       <c r="Q57" s="3">
+        <v>600</v>
+      </c>
+      <c r="R57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1500</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4260,8 +4391,11 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4290,7 +4424,7 @@
         <v>600</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4314,13 +4448,13 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3">
         <v>200</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
+      <c r="V58" s="3">
+        <v>200</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
@@ -4340,25 +4474,28 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>800</v>
-      </c>
-      <c r="H59" s="3">
-        <v>500</v>
       </c>
       <c r="I59" s="3">
         <v>500</v>
@@ -4367,41 +4504,41 @@
         <v>500</v>
       </c>
       <c r="K59" s="3">
+        <v>500</v>
+      </c>
+      <c r="L59" s="3">
         <v>2000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1200</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4420,68 +4557,71 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E60" s="3">
         <v>2600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2900</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4500,38 +4640,41 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>700</v>
+      </c>
+      <c r="E61" s="3">
         <v>800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1900</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4545,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>100</v>
@@ -4554,14 +4697,14 @@
         <v>100</v>
       </c>
       <c r="T61" s="3">
+        <v>100</v>
+      </c>
+      <c r="U61" s="3">
         <v>300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>400</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4580,8 +4723,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4589,16 +4735,16 @@
         <v>300</v>
       </c>
       <c r="E62" s="3">
+        <v>300</v>
+      </c>
+      <c r="F62" s="3">
         <v>200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>100</v>
       </c>
       <c r="G62" s="3">
         <v>100</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+      <c r="H62" s="3">
+        <v>100</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -4609,39 +4755,39 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>2000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3300</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4660,8 +4806,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4740,8 +4889,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4820,8 +4972,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4900,8 +5055,11 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4909,59 +5067,59 @@
         <v>3700</v>
       </c>
       <c r="E66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F66" s="3">
         <v>4300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6900</v>
-      </c>
-      <c r="M66" s="3">
-        <v>5900</v>
       </c>
       <c r="N66" s="3">
         <v>5900</v>
       </c>
       <c r="O66" s="3">
+        <v>5900</v>
+      </c>
+      <c r="P66" s="3">
         <v>4900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6500</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4980,8 +5138,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5010,8 +5171,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5090,8 +5252,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5170,8 +5335,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5250,8 +5418,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5330,62 +5501,65 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-114600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-109600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-105500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-101000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-89000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-85000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-79000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-73100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-67400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-62800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-58300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-53100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-47400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-43900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-39900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-35000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-30000</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5401,8 +5575,8 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z72" s="3">
-        <v>0</v>
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA72" s="3">
         <v>0</v>
@@ -5410,8 +5584,11 @@
       <c r="AB72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5490,8 +5667,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5570,8 +5750,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5650,68 +5833,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E76" s="3">
         <v>21900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>25600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>29400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>34300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>37500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>22300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>24700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>26500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3300</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5730,8 +5916,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5810,79 +5999,82 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5895,74 +6087,77 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2500</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5975,8 +6170,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6005,8 +6203,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6032,10 +6231,10 @@
         <v>200</v>
       </c>
       <c r="K83" s="3">
+        <v>200</v>
+      </c>
+      <c r="L83" s="3">
         <v>100</v>
-      </c>
-      <c r="L83" s="3">
-        <v>200</v>
       </c>
       <c r="M83" s="3">
         <v>200</v>
@@ -6053,23 +6252,23 @@
         <v>200</v>
       </c>
       <c r="R83" s="3">
+        <v>200</v>
+      </c>
+      <c r="S83" s="3">
         <v>300</v>
-      </c>
-      <c r="S83" s="3">
-        <v>200</v>
       </c>
       <c r="T83" s="3">
         <v>200</v>
       </c>
       <c r="U83" s="3">
+        <v>200</v>
+      </c>
+      <c r="V83" s="3">
         <v>600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>200</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6085,8 +6284,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6165,8 +6367,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6245,8 +6450,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6325,8 +6533,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6405,8 +6616,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6485,71 +6699,74 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4000</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-4600</v>
       </c>
       <c r="J89" s="3">
         <v>-4600</v>
       </c>
       <c r="K89" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="L89" s="3">
         <v>-5800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2400</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-3000</v>
       </c>
       <c r="S89" s="3">
         <v>-3000</v>
       </c>
       <c r="T89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="U89" s="3">
         <v>-500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>200</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6565,8 +6782,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6595,8 +6815,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6604,61 +6825,61 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>-100</v>
       </c>
       <c r="P91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -6675,8 +6896,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6755,8 +6979,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6835,70 +7062,73 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>1600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1300</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-4700</v>
       </c>
       <c r="R94" s="3">
         <v>-4700</v>
       </c>
       <c r="S94" s="3">
-        <v>0</v>
+        <v>-4700</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
@@ -6915,8 +7145,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6945,8 +7178,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6974,8 +7208,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7025,8 +7259,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7105,8 +7342,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7185,8 +7425,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7265,8 +7508,11 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7274,62 +7520,62 @@
         <v>-100</v>
       </c>
       <c r="E100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F100" s="3">
         <v>13700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>15100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>5400</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-100</v>
       </c>
       <c r="J100" s="3">
         <v>-100</v>
       </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O100" s="3">
         <v>-100</v>
       </c>
       <c r="P100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q100" s="3">
         <v>18500</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>26700</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>1600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>200</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7345,8 +7591,11 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7374,8 +7623,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7425,71 +7674,74 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3500</v>
-      </c>
-      <c r="E102" s="3">
-        <v>10400</v>
       </c>
       <c r="F102" s="3">
         <v>10400</v>
       </c>
       <c r="G102" s="3">
+        <v>10400</v>
+      </c>
+      <c r="H102" s="3">
         <v>-3000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-7100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>23600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>300</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7503,6 +7755,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LGVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="92">
   <si>
     <t>LGVN</t>
   </si>
@@ -656,110 +656,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
@@ -772,77 +773,80 @@
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
         <v>400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>800</v>
-      </c>
-      <c r="G8" s="3">
-        <v>500</v>
       </c>
       <c r="H8" s="3">
         <v>500</v>
       </c>
       <c r="I8" s="3">
+        <v>500</v>
+      </c>
+      <c r="J8" s="3">
         <v>100</v>
-      </c>
-      <c r="J8" s="3">
-        <v>200</v>
       </c>
       <c r="K8" s="3">
         <v>200</v>
       </c>
       <c r="L8" s="3">
+        <v>200</v>
+      </c>
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>400</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>200</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
       </c>
       <c r="S8" s="3">
+        <v>200</v>
+      </c>
+      <c r="T8" s="3">
         <v>500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3800</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,13 +859,16 @@
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
@@ -873,10 +880,10 @@
         <v>100</v>
       </c>
       <c r="H9" s="3">
+        <v>100</v>
+      </c>
+      <c r="I9" s="3">
         <v>200</v>
-      </c>
-      <c r="I9" s="3">
-        <v>100</v>
       </c>
       <c r="J9" s="3">
         <v>100</v>
@@ -885,7 +892,7 @@
         <v>100</v>
       </c>
       <c r="L9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M9" s="3">
         <v>200</v>
@@ -894,38 +901,38 @@
         <v>200</v>
       </c>
       <c r="O9" s="3">
+        <v>200</v>
+      </c>
+      <c r="P9" s="3">
         <v>300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>200</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>100</v>
       </c>
       <c r="R9" s="3">
         <v>100</v>
       </c>
       <c r="S9" s="3">
+        <v>100</v>
+      </c>
+      <c r="T9" s="3">
         <v>300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2600</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
@@ -938,31 +945,34 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
         <v>300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>700</v>
-      </c>
-      <c r="G10" s="3">
-        <v>300</v>
       </c>
       <c r="H10" s="3">
         <v>300</v>
       </c>
       <c r="I10" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3">
         <v>100</v>
@@ -971,44 +981,44 @@
         <v>100</v>
       </c>
       <c r="M10" s="3">
+        <v>100</v>
+      </c>
+      <c r="N10" s="3">
         <v>-100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>100</v>
-      </c>
-      <c r="O10" s="3">
-        <v>200</v>
       </c>
       <c r="P10" s="3">
         <v>200</v>
       </c>
       <c r="Q10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R10" s="3">
         <v>100</v>
       </c>
       <c r="S10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T10" s="3">
         <v>200</v>
       </c>
       <c r="U10" s="3">
+        <v>200</v>
+      </c>
+      <c r="V10" s="3">
         <v>500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1200</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1021,8 +1031,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1052,77 +1065,78 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E12" s="3">
         <v>2500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1700</v>
-      </c>
-      <c r="H12" s="3">
-        <v>2200</v>
       </c>
       <c r="I12" s="3">
         <v>2200</v>
       </c>
       <c r="J12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K12" s="3">
         <v>1800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1700</v>
-      </c>
-      <c r="R12" s="3">
-        <v>2000</v>
       </c>
       <c r="S12" s="3">
         <v>2000</v>
       </c>
       <c r="T12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U12" s="3">
         <v>1400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1400</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1135,8 +1149,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1218,8 +1235,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1238,20 +1258,20 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>600</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>-100</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>-100</v>
       </c>
       <c r="M14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1272,11 +1292,11 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-300</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1292,8 +1312,8 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1301,16 +1321,19 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>300</v>
+      </c>
+      <c r="E15" s="3">
         <v>400</v>
-      </c>
-      <c r="E15" s="3">
-        <v>200</v>
       </c>
       <c r="F15" s="3">
         <v>200</v>
@@ -1319,10 +1342,10 @@
         <v>200</v>
       </c>
       <c r="H15" s="3">
+        <v>200</v>
+      </c>
+      <c r="I15" s="3">
         <v>300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>200</v>
       </c>
       <c r="J15" s="3">
         <v>200</v>
@@ -1334,7 +1357,7 @@
         <v>200</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1384,8 +1407,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1412,77 +1438,78 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E17" s="3">
         <v>5600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6300</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1495,77 +1522,80 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,8 +1608,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1609,59 +1642,60 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1669,16 +1703,16 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
+      <c r="Y20" s="3">
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
@@ -1692,77 +1726,80 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="S21" s="3">
         <v>-4600</v>
       </c>
-      <c r="E21" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-4400</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1775,8 +1812,11 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1810,17 +1850,17 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1828,11 +1868,11 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1843,8 +1883,8 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
@@ -1858,8 +1898,11 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1867,68 +1910,68 @@
         <v>-5000</v>
       </c>
       <c r="E23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-4100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1941,8 +1984,11 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1973,8 +2019,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2024,8 +2070,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2107,8 +2156,11 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2116,68 +2168,68 @@
         <v>-5000</v>
       </c>
       <c r="E26" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-4100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2190,8 +2242,11 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2199,68 +2254,68 @@
         <v>-5000</v>
       </c>
       <c r="E27" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-4100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2273,8 +2328,11 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2356,8 +2414,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2439,8 +2500,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2522,8 +2586,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2605,59 +2672,62 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
-        <v>200</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2665,16 +2735,16 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
+      <c r="Y32" s="3">
+        <v>0</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
@@ -2688,8 +2758,11 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2697,68 +2770,68 @@
         <v>-5000</v>
       </c>
       <c r="E33" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-4100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2771,8 +2844,11 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2854,8 +2930,11 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2863,68 +2942,68 @@
         <v>-5000</v>
       </c>
       <c r="E35" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-4100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2937,82 +3016,85 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3025,8 +3107,11 @@
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3056,8 +3141,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3087,71 +3173,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E41" s="3">
         <v>14300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>20200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>22100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>25700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>16800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>24500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1400</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3170,8 +3257,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3188,44 +3278,44 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
         <v>400</v>
       </c>
       <c r="J42" s="3">
+        <v>400</v>
+      </c>
+      <c r="K42" s="3">
         <v>2000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>8700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>6800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>8400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>9400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>9200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>4600</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3241,8 +3331,8 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
@@ -3253,8 +3343,11 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3262,19 +3355,19 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
         <v>100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>400</v>
-      </c>
-      <c r="G43" s="3">
-        <v>200</v>
       </c>
       <c r="H43" s="3">
         <v>200</v>
       </c>
       <c r="I43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J43" s="3">
         <v>100</v>
@@ -3286,13 +3379,13 @@
         <v>100</v>
       </c>
       <c r="M43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N43" s="3">
         <v>200</v>
       </c>
       <c r="O43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P43" s="3">
         <v>100</v>
@@ -3301,23 +3394,23 @@
         <v>100</v>
       </c>
       <c r="R43" s="3">
+        <v>100</v>
+      </c>
+      <c r="S43" s="3">
         <v>200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>100</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
       <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
         <v>400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>700</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3336,8 +3429,11 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3368,8 +3464,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3419,8 +3515,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3451,39 +3550,39 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3502,71 +3601,74 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E46" s="3">
         <v>15300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>20300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>23200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>28200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>31900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>35400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>19700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>22100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>25300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2200</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,8 +3687,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3617,8 +3722,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3668,71 +3773,74 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>3800</v>
       </c>
       <c r="J48" s="3">
         <v>3800</v>
       </c>
       <c r="K48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="L48" s="3">
         <v>4100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5900</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3751,8 +3859,11 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3760,28 +3871,28 @@
         <v>2300</v>
       </c>
       <c r="E49" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F49" s="3">
         <v>2400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2400</v>
-      </c>
-      <c r="H49" s="3">
-        <v>2300</v>
       </c>
       <c r="I49" s="3">
         <v>2300</v>
       </c>
       <c r="J49" s="3">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="K49" s="3">
         <v>2500</v>
       </c>
       <c r="L49" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="M49" s="3">
         <v>2400</v>
@@ -3796,16 +3907,16 @@
         <v>2400</v>
       </c>
       <c r="Q49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="R49" s="3">
         <v>2300</v>
-      </c>
-      <c r="R49" s="3">
-        <v>2400</v>
       </c>
       <c r="S49" s="3">
         <v>2400</v>
       </c>
       <c r="T49" s="3">
-        <v>1500</v>
+        <v>2400</v>
       </c>
       <c r="U49" s="3">
         <v>1500</v>
@@ -3813,8 +3924,8 @@
       <c r="V49" s="3">
         <v>1500</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
+      <c r="W49" s="3">
+        <v>1500</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
@@ -3834,8 +3945,11 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3917,8 +4031,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4000,8 +4117,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4062,8 +4182,8 @@
       <c r="V52" s="3">
         <v>200</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
+      <c r="W52" s="3">
+        <v>200</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
@@ -4083,8 +4203,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4166,71 +4289,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E54" s="3">
         <v>20800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>29900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>19400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>30500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>39200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>42800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>27200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>29900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9800</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4249,8 +4375,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4280,8 +4409,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4311,71 +4441,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
-      </c>
-      <c r="P57" s="3">
-        <v>600</v>
       </c>
       <c r="Q57" s="3">
         <v>600</v>
       </c>
       <c r="R57" s="3">
+        <v>600</v>
+      </c>
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1500</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4394,8 +4525,11 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4427,7 +4561,7 @@
         <v>600</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4451,13 +4585,13 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V58" s="3">
         <v>200</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
+      <c r="W58" s="3">
+        <v>200</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
@@ -4477,28 +4611,31 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
         <v>100</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
       <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>800</v>
-      </c>
-      <c r="I59" s="3">
-        <v>500</v>
       </c>
       <c r="J59" s="3">
         <v>500</v>
@@ -4507,41 +4644,41 @@
         <v>500</v>
       </c>
       <c r="L59" s="3">
+        <v>500</v>
+      </c>
+      <c r="M59" s="3">
         <v>2000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1200</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4560,71 +4697,74 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E60" s="3">
         <v>2700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2900</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4643,41 +4783,44 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>500</v>
+      </c>
+      <c r="E61" s="3">
         <v>700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1900</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4691,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S61" s="3">
         <v>100</v>
@@ -4700,14 +4843,14 @@
         <v>100</v>
       </c>
       <c r="U61" s="3">
+        <v>100</v>
+      </c>
+      <c r="V61" s="3">
         <v>300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>400</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4726,8 +4869,11 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4738,16 +4884,16 @@
         <v>300</v>
       </c>
       <c r="F62" s="3">
+        <v>300</v>
+      </c>
+      <c r="G62" s="3">
         <v>200</v>
-      </c>
-      <c r="G62" s="3">
-        <v>100</v>
       </c>
       <c r="H62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+      <c r="I62" s="3">
+        <v>100</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -4758,39 +4904,39 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>2000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3300</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4809,8 +4955,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4892,8 +5041,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4975,8 +5127,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5058,71 +5213,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3700</v>
+        <v>4100</v>
       </c>
       <c r="E66" s="3">
         <v>3700</v>
       </c>
       <c r="F66" s="3">
+        <v>3700</v>
+      </c>
+      <c r="G66" s="3">
         <v>4300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6900</v>
-      </c>
-      <c r="N66" s="3">
-        <v>5900</v>
       </c>
       <c r="O66" s="3">
         <v>5900</v>
       </c>
       <c r="P66" s="3">
+        <v>5900</v>
+      </c>
+      <c r="Q66" s="3">
         <v>4900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6500</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5141,8 +5299,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5172,8 +5333,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5255,8 +5417,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5338,8 +5503,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5421,8 +5589,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5504,65 +5675,68 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-119600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-114600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-109600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-105500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-101000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-89000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-85000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-79000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-73100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-67400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-62800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-58300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-53100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-47400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-43900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-39900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-35000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-30000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5578,8 +5752,8 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA72" s="3">
-        <v>0</v>
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB72" s="3">
         <v>0</v>
@@ -5587,8 +5761,11 @@
       <c r="AC72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5670,8 +5847,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5753,8 +5933,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5836,71 +6019,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E76" s="3">
         <v>17200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>24600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>29400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>34300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>37500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>22300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>24700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>26500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3300</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5919,8 +6105,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6002,82 +6191,85 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6090,8 +6282,11 @@
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6099,68 +6294,68 @@
         <v>-5000</v>
       </c>
       <c r="E81" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-4100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6173,8 +6368,11 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6204,8 +6402,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6234,10 +6433,10 @@
         <v>200</v>
       </c>
       <c r="L83" s="3">
+        <v>200</v>
+      </c>
+      <c r="M83" s="3">
         <v>100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>200</v>
       </c>
       <c r="N83" s="3">
         <v>200</v>
@@ -6255,23 +6454,23 @@
         <v>200</v>
       </c>
       <c r="S83" s="3">
+        <v>200</v>
+      </c>
+      <c r="T83" s="3">
         <v>300</v>
-      </c>
-      <c r="T83" s="3">
-        <v>200</v>
       </c>
       <c r="U83" s="3">
         <v>200</v>
       </c>
       <c r="V83" s="3">
+        <v>200</v>
+      </c>
+      <c r="W83" s="3">
         <v>600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>200</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6287,8 +6486,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6370,8 +6572,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6453,8 +6658,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6536,8 +6744,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6619,8 +6830,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6702,74 +6916,77 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4000</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-4600</v>
       </c>
       <c r="K89" s="3">
         <v>-4600</v>
       </c>
       <c r="L89" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="M89" s="3">
         <v>-5800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2400</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-3000</v>
       </c>
       <c r="T89" s="3">
         <v>-3000</v>
       </c>
       <c r="U89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="V89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>200</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6785,8 +7002,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6816,73 +7036,74 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1200</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
+      <c r="X91" s="3">
+        <v>0</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
@@ -6899,8 +7120,11 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6982,8 +7206,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7065,73 +7292,76 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>1600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1300</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-4700</v>
       </c>
       <c r="S94" s="3">
         <v>-4700</v>
       </c>
       <c r="T94" s="3">
-        <v>0</v>
+        <v>-4700</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
+      <c r="X94" s="3">
+        <v>0</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
@@ -7148,8 +7378,11 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7179,8 +7412,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7211,8 +7445,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7262,8 +7496,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7345,8 +7582,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7428,8 +7668,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7511,8 +7754,11 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7523,62 +7769,62 @@
         <v>-100</v>
       </c>
       <c r="F100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G100" s="3">
         <v>13700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>15100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5400</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-100</v>
       </c>
       <c r="K100" s="3">
         <v>-100</v>
       </c>
       <c r="L100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P100" s="3">
         <v>-100</v>
       </c>
       <c r="Q100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R100" s="3">
         <v>18500</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>26700</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>1600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>200</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7594,8 +7840,11 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7626,8 +7875,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7677,74 +7926,77 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3500</v>
-      </c>
-      <c r="F102" s="3">
-        <v>10400</v>
       </c>
       <c r="G102" s="3">
         <v>10400</v>
       </c>
       <c r="H102" s="3">
+        <v>10400</v>
+      </c>
+      <c r="I102" s="3">
         <v>-3000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>23600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>300</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7758,6 +8010,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LGVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="92">
   <si>
     <t>LGVN</t>
   </si>
@@ -656,121 +656,122 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
@@ -780,86 +781,92 @@
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>400</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
-      </c>
-      <c r="N8" s="3">
-        <v>300</v>
-      </c>
-      <c r="O8" s="3">
-        <v>100</v>
       </c>
       <c r="P8" s="3">
         <v>300</v>
       </c>
       <c r="Q8" s="3">
+        <v>100</v>
+      </c>
+      <c r="R8" s="3">
+        <v>300</v>
+      </c>
+      <c r="S8" s="3">
         <v>500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>4400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>3800</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
@@ -869,22 +876,28 @@
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3">
+        <v>100</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
         <v>200</v>
-      </c>
-      <c r="F9" s="3">
-        <v>100</v>
-      </c>
-      <c r="G9" s="3">
-        <v>100</v>
       </c>
       <c r="H9" s="3">
         <v>100</v>
@@ -893,62 +906,62 @@
         <v>100</v>
       </c>
       <c r="J9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K9" s="3">
         <v>100</v>
       </c>
       <c r="L9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M9" s="3">
         <v>100</v>
       </c>
       <c r="N9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P9" s="3">
         <v>200</v>
       </c>
       <c r="Q9" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R9" s="3">
         <v>200</v>
       </c>
       <c r="S9" s="3">
+        <v>300</v>
+      </c>
+      <c r="T9" s="3">
+        <v>200</v>
+      </c>
+      <c r="U9" s="3">
         <v>100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>3200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2600</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
@@ -958,85 +971,91 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>300</v>
+      </c>
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>300</v>
       </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3">
-        <v>100</v>
-      </c>
       <c r="M10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N10" s="3">
         <v>100</v>
       </c>
       <c r="O10" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="P10" s="3">
         <v>100</v>
       </c>
       <c r="Q10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R10" s="3">
+        <v>100</v>
+      </c>
+      <c r="S10" s="3">
         <v>200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>500</v>
-      </c>
-      <c r="X10" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>600</v>
       </c>
       <c r="Z10" s="3">
         <v>1200</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
+      <c r="AA10" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>1200</v>
       </c>
       <c r="AC10" s="3" t="s">
         <v>3</v>
@@ -1047,8 +1066,14 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1080,86 +1105,88 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F12" s="3">
         <v>3900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>3000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>2500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>2000</v>
-      </c>
-      <c r="H12" s="3">
-        <v>2200</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1700</v>
       </c>
       <c r="J12" s="3">
         <v>2200</v>
       </c>
       <c r="K12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L12" s="3">
         <v>2200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N12" s="3">
         <v>1800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>2300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>2800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>3300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>3000</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>1700</v>
-      </c>
-      <c r="R12" s="3">
-        <v>1300</v>
       </c>
       <c r="S12" s="3">
         <v>1700</v>
       </c>
       <c r="T12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V12" s="3">
         <v>2000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>2000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>1400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>1500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>1400</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1169,8 +1196,14 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1258,16 +1291,22 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>-200</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1284,24 +1323,24 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1318,14 +1357,14 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-300</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1338,17 +1377,23 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1359,25 +1404,25 @@
         <v>300</v>
       </c>
       <c r="F15" s="3">
+        <v>300</v>
+      </c>
+      <c r="G15" s="3">
+        <v>300</v>
+      </c>
+      <c r="H15" s="3">
         <v>400</v>
-      </c>
-      <c r="G15" s="3">
-        <v>200</v>
-      </c>
-      <c r="H15" s="3">
-        <v>200</v>
       </c>
       <c r="I15" s="3">
         <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>200</v>
       </c>
       <c r="L15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M15" s="3">
         <v>200</v>
@@ -1386,10 +1431,10 @@
         <v>200</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1436,8 +1481,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1466,86 +1517,88 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F17" s="3">
         <v>7400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>5600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>5500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>5300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>5900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>5000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>5400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>5500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>4200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>5100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>5600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>6800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>6300</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1555,86 +1608,92 @@
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-7300</v>
+        <v>-4800</v>
       </c>
       <c r="E18" s="3">
         <v>-5400</v>
       </c>
       <c r="F18" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="H18" s="3">
         <v>-5200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-4300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-4600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-4100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-5400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-5200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-5700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-4700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-5300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-4200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-3400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-4000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-4900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-5100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-3100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-1400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1644,8 +1703,14 @@
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1677,8 +1742,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1686,76 +1753,76 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>600</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>800</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-1400</v>
       </c>
       <c r="R20" s="3">
         <v>-100</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="T20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
@@ -1766,86 +1833,92 @@
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-7100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-4800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-4800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-3800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-4400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-3200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-5200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-4900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-5500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-4500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-4200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-5400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-3300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-3800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-4600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-4800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-2900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-1200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1855,8 +1928,14 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1896,32 +1975,32 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -1929,11 +2008,11 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>3</v>
@@ -1944,86 +2023,92 @@
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-7200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-5000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-5000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-4100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-4400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-3400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-4100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-6000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-5100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-5600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-4600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-4500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-5600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-3500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-4100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-4900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-5000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-3100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2033,8 +2118,14 @@
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2071,11 +2162,11 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2122,8 +2213,14 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2211,86 +2308,92 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-7200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-5000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-5000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-4100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-4400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-3400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-4100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-6000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-5100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-5600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-4600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-4500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-5600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-3500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-4100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-4900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-5000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-3100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2300,86 +2403,92 @@
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-7200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-5000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-5000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-4100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-4600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-11900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-4100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-6000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-5900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-5600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-4600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-4500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-5600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-3500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-4100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-4900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-5000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-3100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2389,8 +2498,14 @@
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2478,8 +2593,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2567,8 +2688,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2656,8 +2783,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2745,8 +2878,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2754,76 +2893,76 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-800</v>
-      </c>
-      <c r="P32" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>1400</v>
       </c>
       <c r="R32" s="3">
         <v>100</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="T32" s="3">
+        <v>100</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
@@ -2834,86 +2973,92 @@
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-7200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-5000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-5000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-4100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-4400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-3400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-4100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-6000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-5100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-5600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-4600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-4500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-5600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-3500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-4100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-4900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-5000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-3100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2923,8 +3068,14 @@
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3012,86 +3163,92 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-7200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-5000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-5000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-4100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-4400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-3400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-4100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-6000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-5100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-5600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-4600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-4500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-5600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-3500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-4100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-4900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-5000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-3100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3101,91 +3258,97 @@
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3195,8 +3358,14 @@
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3228,8 +3397,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3261,80 +3432,82 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F41" s="3">
         <v>9200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>10300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>14300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>19200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>22800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>12400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>4900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>5000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>10500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>13600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>20200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>22100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>25700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>9700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>16800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>24500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1400</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3523,14 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3374,47 +3553,47 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>2000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>5900</v>
-      </c>
-      <c r="N42" s="3">
-        <v>8700</v>
-      </c>
-      <c r="O42" s="3">
-        <v>9200</v>
       </c>
       <c r="P42" s="3">
         <v>8700</v>
       </c>
       <c r="Q42" s="3">
+        <v>9200</v>
+      </c>
+      <c r="R42" s="3">
+        <v>8700</v>
+      </c>
+      <c r="S42" s="3">
         <v>6800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>8400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>9400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>9200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>4600</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3427,11 +3606,11 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -3439,8 +3618,14 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3448,28 +3633,28 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>200</v>
-      </c>
-      <c r="K43" s="3">
-        <v>100</v>
-      </c>
-      <c r="L43" s="3">
-        <v>100</v>
       </c>
       <c r="M43" s="3">
         <v>100</v>
@@ -3478,41 +3663,41 @@
         <v>100</v>
       </c>
       <c r="O43" s="3">
+        <v>100</v>
+      </c>
+      <c r="P43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q43" s="3">
         <v>200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>200</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>100</v>
-      </c>
-      <c r="R43" s="3">
-        <v>100</v>
       </c>
       <c r="S43" s="3">
         <v>100</v>
       </c>
       <c r="T43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U43" s="3">
         <v>100</v>
       </c>
       <c r="V43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W43" s="3">
+        <v>100</v>
+      </c>
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
         <v>400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>700</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3528,8 +3713,14 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3566,11 +3757,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3617,8 +3808,14 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3655,42 +3852,42 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>500</v>
-      </c>
-      <c r="U45" s="3">
-        <v>600</v>
-      </c>
-      <c r="V45" s="3">
-        <v>800</v>
       </c>
       <c r="W45" s="3">
         <v>600</v>
       </c>
       <c r="X45" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3706,80 +3903,86 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F46" s="3">
         <v>10300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>11300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>15300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>19600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>23800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>13400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>5800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>5000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>10300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>14900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>20300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>23200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>28200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>31900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>35400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>19700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>22100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>25300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>2200</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3795,8 +3998,14 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3833,11 +4042,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3884,49 +4093,55 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F48" s="3">
         <v>2700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4300</v>
-      </c>
-      <c r="O48" s="3">
-        <v>4500</v>
-      </c>
-      <c r="P48" s="3">
-        <v>4700</v>
       </c>
       <c r="Q48" s="3">
         <v>4500</v>
@@ -3935,29 +4150,29 @@
         <v>4700</v>
       </c>
       <c r="S48" s="3">
+        <v>4500</v>
+      </c>
+      <c r="T48" s="3">
+        <v>4700</v>
+      </c>
+      <c r="U48" s="3">
         <v>4900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>5000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>5200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>5400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>5700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>5900</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3973,13 +4188,19 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="E49" s="3">
         <v>2300</v>
@@ -3988,7 +4209,7 @@
         <v>2300</v>
       </c>
       <c r="G49" s="3">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="H49" s="3">
         <v>2300</v>
@@ -4000,19 +4221,19 @@
         <v>2300</v>
       </c>
       <c r="K49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L49" s="3">
         <v>2300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N49" s="3">
         <v>2500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2500</v>
-      </c>
-      <c r="N49" s="3">
-        <v>2400</v>
-      </c>
-      <c r="O49" s="3">
-        <v>2400</v>
       </c>
       <c r="P49" s="3">
         <v>2400</v>
@@ -4024,28 +4245,28 @@
         <v>2400</v>
       </c>
       <c r="S49" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="T49" s="3">
         <v>2400</v>
       </c>
       <c r="U49" s="3">
+        <v>2300</v>
+      </c>
+      <c r="V49" s="3">
         <v>2400</v>
       </c>
-      <c r="V49" s="3">
-        <v>1500</v>
-      </c>
       <c r="W49" s="3">
-        <v>1500</v>
+        <v>2400</v>
       </c>
       <c r="X49" s="3">
         <v>1500</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z49" s="3" t="s">
-        <v>3</v>
+      <c r="Y49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>1500</v>
       </c>
       <c r="AA49" s="3" t="s">
         <v>3</v>
@@ -4062,8 +4283,14 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4151,8 +4378,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4240,13 +4473,19 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
@@ -4308,11 +4547,11 @@
       <c r="X52" s="3">
         <v>200</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
+      <c r="Y52" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>200</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
@@ -4329,8 +4568,14 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4418,80 +4663,86 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F54" s="3">
         <v>15600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>16700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>20800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>25600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>29900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>19400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>9700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>12100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>11600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>17100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>21800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>27400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>30500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>35300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>39200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>42800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>27200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>29900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>32400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>9200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>9800</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4507,8 +4758,14 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4540,8 +4797,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4573,80 +4832,82 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>400</v>
+      </c>
+      <c r="F57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>900</v>
-      </c>
-      <c r="I57" s="3">
-        <v>600</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1500</v>
       </c>
       <c r="K57" s="3">
         <v>600</v>
       </c>
       <c r="L57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M57" s="3">
+        <v>600</v>
+      </c>
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1700</v>
-      </c>
-      <c r="N57" s="3">
-        <v>500</v>
-      </c>
-      <c r="O57" s="3">
-        <v>1800</v>
       </c>
       <c r="P57" s="3">
         <v>500</v>
       </c>
       <c r="Q57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R57" s="3">
+        <v>500</v>
+      </c>
+      <c r="S57" s="3">
         <v>300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1500</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4662,16 +4923,22 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E58" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F58" s="3">
         <v>600</v>
@@ -4701,10 +4968,10 @@
         <v>600</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4725,17 +4992,17 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>200</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4751,19 +5018,25 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
       </c>
       <c r="F59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3">
         <v>0</v>
@@ -4772,59 +5045,59 @@
         <v>100</v>
       </c>
       <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>100</v>
+      </c>
+      <c r="K59" s="3">
         <v>400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>800</v>
-      </c>
-      <c r="K59" s="3">
-        <v>500</v>
-      </c>
-      <c r="L59" s="3">
-        <v>500</v>
       </c>
       <c r="M59" s="3">
         <v>500</v>
       </c>
       <c r="N59" s="3">
+        <v>500</v>
+      </c>
+      <c r="O59" s="3">
+        <v>500</v>
+      </c>
+      <c r="P59" s="3">
         <v>2000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>3200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>2100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>2000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>2100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1200</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4840,80 +5113,86 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F60" s="3">
         <v>4900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>4900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>2800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>3800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>2900</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4929,50 +5208,56 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>200</v>
+      </c>
+      <c r="F61" s="3">
         <v>300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4983,26 +5268,26 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V61" s="3">
         <v>100</v>
       </c>
       <c r="W61" s="3">
+        <v>100</v>
+      </c>
+      <c r="X61" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y61" s="3">
         <v>300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>400</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5018,13 +5303,19 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E62" s="3">
         <v>300</v>
@@ -5036,62 +5327,62 @@
         <v>300</v>
       </c>
       <c r="H62" s="3">
+        <v>300</v>
+      </c>
+      <c r="I62" s="3">
+        <v>300</v>
+      </c>
+      <c r="J62" s="3">
         <v>200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>2000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>3000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>3100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>3300</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5107,8 +5398,14 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5196,8 +5493,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5285,8 +5588,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5374,80 +5683,86 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F66" s="3">
         <v>5600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>5000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>5800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>5500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>6900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>5900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>5900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>4900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>5300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>4800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>5200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>5900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>7300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>6500</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5463,8 +5778,14 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5496,8 +5817,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5585,8 +5908,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5674,8 +6003,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5763,8 +6098,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5852,74 +6193,80 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-137000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-132300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-126900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-119600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-114600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-109600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-105500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-101000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-89000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-85000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-79000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-73100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-67400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-62800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-58300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-53100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-47400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-43900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-39900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-35000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-30000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5932,17 +6279,23 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>0</v>
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6030,8 +6383,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6119,8 +6478,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6208,80 +6573,86 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F76" s="3">
         <v>10000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>12700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>17200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>21900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>25600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>14900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>6700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>6600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>11300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>16300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>20500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>24600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>29400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>34300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>37500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>22300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>24700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>26500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>2000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>3300</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6297,8 +6668,14 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6386,91 +6763,97 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6480,86 +6863,92 @@
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-7200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-5000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-5000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-4100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-4400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-3400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-4100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-6000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-5100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-5600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-4600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-4500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-5600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-3500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-4100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-4900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-5000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-3100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6569,8 +6958,14 @@
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6602,8 +6997,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6638,13 +7035,13 @@
         <v>200</v>
       </c>
       <c r="N83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>200</v>
       </c>
       <c r="P83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
@@ -6659,25 +7056,25 @@
         <v>200</v>
       </c>
       <c r="U83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>200</v>
       </c>
       <c r="W83" s="3">
+        <v>300</v>
+      </c>
+      <c r="X83" s="3">
         <v>200</v>
-      </c>
-      <c r="X83" s="3">
-        <v>600</v>
       </c>
       <c r="Y83" s="3">
         <v>200</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
+      <c r="Z83" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>200</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
@@ -6691,8 +7088,14 @@
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6780,8 +7183,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6869,8 +7278,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6958,8 +7373,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7047,8 +7468,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7136,83 +7563,89 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-3600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-4700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-4600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-4000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-4600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-4600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-5800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2300</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-3300</v>
       </c>
       <c r="R89" s="3">
         <v>-4200</v>
       </c>
       <c r="S89" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="T89" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="U89" s="3">
         <v>-1300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-2400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-3000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-3000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>200</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7225,8 +7658,14 @@
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7258,31 +7697,33 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-400</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-200</v>
@@ -7291,49 +7732,49 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-1200</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
+      <c r="AA91" s="3">
+        <v>0</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
@@ -7347,8 +7788,14 @@
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7436,8 +7883,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7525,82 +7978,88 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-500</v>
       </c>
       <c r="I94" s="3">
         <v>-100</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="K94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>1600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>3800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>2500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>1500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-4700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-4700</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-200</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
+      <c r="AA94" s="3">
+        <v>0</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
@@ -7614,8 +8073,14 @@
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7647,8 +8112,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7685,11 +8152,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7736,8 +8203,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7825,8 +8298,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7914,8 +8393,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8003,83 +8488,89 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>800</v>
+      </c>
+      <c r="F100" s="3">
         <v>4100</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-100</v>
       </c>
       <c r="G100" s="3">
         <v>-100</v>
       </c>
       <c r="H100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J100" s="3">
         <v>13700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>15100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>5400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>18500</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>26700</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>1600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>200</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8092,8 +8583,14 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8130,11 +8627,11 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8181,83 +8678,89 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-4000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-4900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>10400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>10400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-3000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>3000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-2200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-5500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-3100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-3500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>15900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-7100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-7600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>23600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>300</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8268,6 +8771,12 @@
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
